--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Correções banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções banca'!$A$1:$E$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,13 +30,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00365F91"/>
       </patternFill>
     </fill>
     <fill>
@@ -55,12 +54,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,13 +62,8 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -82,49 +71,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,17 +457,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Membro</t>
@@ -534,22 +500,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>(Capa) O nome do Prof. Maximo é sem acento.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Removido o acento em todas as ocorrências: capa/folha de rosto (tese.tex), agradecimentos, citação da publicação no Cap.1 e entrada do .bib.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Confirmado com o autor. No registro oficial do ITA consta com acento; adotada a grafia sem acento conforme pedido da banca e conforme o professor assina suas publicações.</t>
         </is>
@@ -561,22 +527,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Fazer um Resumo e um Abstract mais didáticos; do jeito que estão, leigos não entenderão e poderão desistir da leitura.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Resumo e Abstract inteiramente reescritos em linguagem acessível: partem do cenário concreto (táxis aéreos e drones sobre cidades), explicam detect-and-avoid e as metades sense/avoid, descrevem os quatro estágios do pipeline em português/inglês simples e só então apresentam os três estudos e seus resultados.</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>PreTextuais/resumo.tex e PreTextuais/abstract.tex. Criado também PreTextuais/resumo_frd.tex, versão condensada, pois o resumo completo não cabe na caixa de altura fixa da Folha de Registro do Documento.</t>
         </is>
@@ -588,22 +554,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>(Pg. 25) Colocar o significado da sigla GNSS na primeira aparição.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Primeira ocorrência (Cap.1, Seção 1.1.1) expandida para "Global Navigation Satellite System (GNSS)".</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>GNSS também acrescentado à Lista de Abreviaturas, que já o continha.</t>
         </is>
@@ -615,22 +581,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>(Pg. 27) Trocar "convolutional neural networks (CNNs)" por "Convolutional Neural Networks (CNNs)".</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Corrigido no Cap.1 e no Cap.2 ("A Convolutional Neural Network (CNN)").</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -638,22 +604,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>(Pg. 27 e 28) Acrescentar na Introdução uma Seção "Proposta de Solução", dividindo a Seção 1.3 em duas.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Seção 1.3 dividida: "1.3 Problem Statement" (problema e as três dificuldades) e a nova "1.4 Proposed Solution", que descreve o pipeline, traz a figura da arquitetura e a subseção "Where the Point Clouds Come From". As seções seguintes foram renumeradas automaticamente.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -661,22 +627,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>(Pg. 30) Elogio à Seção sobre o uso de IA generativa no trabalho.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Sem ação necessária. A seção foi mantida (agora Seção 1.9).</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -688,22 +654,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>(Cap. 2) Ao apresentar as equações, ir dizendo onde elas serão utilizadas mais adiante.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Acrescentada ao final do Cap.2 a seção "Summary and Road Map", que percorre cada equação do capítulo e indica em qual capítulo posterior ela é usada (recursões do KF/EKF, convenções de referencial, perturbação em SE(3), modelo de velocidade constante, medida esférica, projeção pinhole, métricas e blocos de aprendizado). Adicionados também ponteiros pontuais ao longo do texto.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -711,22 +677,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>(Pg. 36 e 37) Trocar "root-mean-square error (RMSE)" por "Root-Mean-Square Error (RMSE)" e o mesmo para NEES, NIS, PCRB, TP, FP, FN, R, MOTA e CNN.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Todas as expansões corrigidas para caixa alta: RMSE, NEES, NIS, PCRB, True Positive (TP), False Positive (FP), False Negative (FN), Precision (P), Recall (R), MOTA, AMOTA, CNN, KF, BEV.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Feita varredura automática em todos os arquivos .tex para localizar o padrão "expansão minúscula (SIGLA)".</t>
         </is>
@@ -738,22 +704,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>(Pg. 43) Primeira linha da Seção 3.3: uma palavra ultrapassa a margem direita.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Corrigido. A frase foi reescrita para eliminar o composto hifenizado que impedia a quebra, e foram acrescentados \tolerance=2000 e \emergencystretch=3em ao preâmbulo.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Efeito global: as linhas com excesso de largura (overfull hbox) caíram de 14 para 1 — a única remanescente está na tabela da Folha de Registro, que é do próprio template do ITA.</t>
         </is>
@@ -765,22 +731,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Finalizar o Capítulo 3 (e todos os capítulos) com um parágrafo breve descrevendo o que será visto no capítulo seguinte.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Acrescentados parágrafos de encerramento com a transição para o capítulo seguinte nos Capítulos 2, 3, 5, 6 e 7. O Capítulo 4 já possuía; o Capítulo 8 é o último.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>No Cap.3 o parágrafo foi reescrito para apontar para o Cap.4 (o capítulo seguinte), e não para o Cap.5.</t>
         </is>
@@ -792,22 +758,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>(Pg. 49) A Figura 4.1 demorou demais para aparecer; deveria estar já no Capítulo 1.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>A figura do pipeline foi inserida no Capítulo 1, dentro da nova Seção 1.4 (Proposed Solution), como Figura 1.2, com legenda remetendo ao Cap.4 para o detalhamento. A figura original foi mantida no Cap.4.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -815,22 +781,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>(Pg. 53) Seções criadas sem texto introdutório antes da primeira subseção (ex.: 5.2 e 5.2.1); ocorre várias vezes no documento.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Localizadas por varredura automática as 12 ocorrências do padrão e inserido um parágrafo introdutório em todas: Cap.1 (Objectives), Cap.2 (3 seções), Cap.3 (2), Cap.5 (2, incluindo a 5.2 citada), Cap.6 (Results) e Cap.7 (3).</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -838,22 +804,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>(Pg. 54) Trocar "Constant-velocity (CV)" por "Constant-Velocity (CV)"; o mesmo para PCRB (pg. 61).</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Corrigido no Cap.2 e no Cap.5, e o PCRB corrigido no Cap.2, Cap.5 e Apêndice A.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -861,22 +827,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Não sou especialista na área e não poderei revisar as equações.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Sem ação. As deduções foram, ainda assim, ampliadas e verificadas em resposta aos apontamentos do Prof. Bruno.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -884,22 +850,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>(Pg. 58) Elogio à formulação e à demonstração formal da Proposição 5.1.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Sem ação. Mantida.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -911,22 +877,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Elogio ao formalismo e aos resultados do Capítulo 5.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -938,22 +904,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>(Pg. 61) Deixar para dizer o que será feito no Capítulo 6 somente no último parágrafo do Capítulo 5, e não na penúltima seção.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>O anúncio do Cap.6 foi removido da Seção 5.6.3 e passou a ser o último parágrafo do capítulo, dentro da nova Seção 5.8 (Choice of Frame in Practice).</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -961,22 +927,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>(Pg. 77) Trocar "normalized innovation squared (NIS)" por caixa alta; idem RPC (pg. 82), PFN (pg. 91) e RMSE (pg. 94).</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Corrigidos: NIS (Cap.2 e Cap.6), Remote-Procedure-Call (RPC) e Pillar Feature Network (PFN) no Cap.7, e RMSE no Cap.7. Acrescentada também Set-Abstraction (SA).</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -984,22 +950,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Os Capítulos 7 e 8 estão adequados; o Capítulo 8 detalha bem limitações e melhorias futuras.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Sem ação corretiva. Ambos foram, mesmo assim, ampliados em resposta aos demais membros.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1011,22 +977,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>O Capítulo 6 está bastante adequado.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Sem ação corretiva. Ampliado conforme pedidos dos Profs. Alberto e Bruno.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1038,22 +1004,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Sugiro incluir o artigo clássico do algoritmo Adam (2014, arXiv).</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Referência de Kingma e Ba (ICLR 2015; arXiv:1412.6980, 2014) adicionada ao .bib e citada nos dois pontos em que o Adam é usado (Cap.7 e Apêndice B).</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1061,22 +1027,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Parabéns pelo excelente trabalho.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1088,22 +1054,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Publicação em conferência Qualis A1; texto bem escrito; uso de IA adequado; boa apresentação.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1115,24 +1081,24 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Slide 35: o gráfico não é igual à Figura 6.6 da dissertação (p. 75). Ajustar na dissertação e explicar melhor a figura no texto.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Investigado e esclarecido. A figura da dissertação JÁ É a versão corrigida: em 6 de junho de 2026 foi feita uma auditoria da geometria e do filtro (commit 09505f0) que constatou que a projeção quadro a quadro sempre esteve correta (mediana 1,05 m) e que o erro maior vinha do modelo de velocidade constante sendo propagado em malha aberta durante as longas lacunas de detecção; a correção foi limitar esse horizonte e reinicializar a trilha por interseção raio-plano após uma lacuna. Os slides da defesa usam a figura ANTERIOR a essa auditoria (verificado por MD5: os PDFs dos slides são idênticos aos do commit eb5cb0a, de 5 de junho). Portanto não há correção a trazer da apresentação para a dissertação: é a apresentação que está desatualizada. O texto foi substancialmente ampliado para explicar a figura, e o episódio foi registrado explicitamente na Seção 6.3.2.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ATENÇÃO: os slides devem ser atualizados antes de qualquer reapresentação. Além disso, a regeneração da figura a partir dos dados brutos NÃO é possível nesta máquina: os estados corrigidos pela auditoria não foram persistidos (os dois tracking_results.npz existentes correspondem à versão anterior à auditoria). Recomenda-se localizar ou reexecutar a auditoria na máquina primária.</t>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Investigado e RESOLVIDO na máquina de dados. A figura da dissertação já era a versão corrigida pela auditoria de 06/06/2026 (commit 09505f0). Os scripts da auditoria estavam versionados no repositório do tracker (commit 4dee191: verify_projection.py, verify_ekf.py, cap6_figs.py) e reproduziram bit a bit todos os números publicados, de modo que as figuras 6.7 e 6.8 foram efetivamente regeradas a partir dos dados brutos (novo script cap6_figs_v2.py).</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Os slides continuam desatualizados e devem ser atualizados antes de qualquer reapresentação; a pasta 'DEFESA - SLIDES' não existe nesta máquina, então a regeração das figuras dos slides não pôde ser feita aqui. Verificada também a suspeita de que a curva de erro seria inconsistente com o gráfico de trajetória: NÃO há inconsistência. As duas foram conferidas amostra a amostra e coincidem exatamente; a aparência de contradição vinha de os estados divergentes (até (40,4; 17,4) m) caírem fora dos limites dos eixos do mapa. Registrado no texto (Seção 6.3.2).</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1108,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>A legenda do EKF na Figura 6.6 está confusa; indicar que corresponde à barra de cor.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Legenda reescrita explicitando que a trajetória do EKF é colorida pelo tempo de voo e que a barra de cor à direita é a escala correspondente.</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1165,22 +1131,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Debater possíveis erros sistemáticos: giro do drone, erro na diagonal, erro devido à distância.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Ampliada a discussão de resultados do Cap.6 com a análise dos erros sistemáticos: dependência do erro com a distância (com a figura de erro versus alcance), efeito do ângulo de depressão rasante e o papel do giro em guinada, que é quando a pose de navegação é menos confiável e o alvo sai do campo de visão.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1188,22 +1154,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Comentário geral: o texto não detalha suficientemente bem os resultados mostrados em gráficos (ex.: Figura 6.7).</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Discussão dos resultados do Cap.6 substancialmente ampliada, separando explicitamente a acurácia da geometria (projeção quadro a quadro) da robustez da cadeia completa, e explicando o que cada painel das figuras mostra.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1211,22 +1177,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Renomear "horizontal error" para "erro no plano do chão" (ground-plane error).</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Termo renomeado para "ground-plane error" em todo o Cap.6 e no Cap.8, e acrescentado um parágrafo "Terminology" explicando que a medida é feita no plano do solo e não no plano da aeronave, e por que a componente vertical não é reportada.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Os rótulos dos eixos dentro dos arquivos PDF das figuras serão atualizados na regeneração.</t>
         </is>
@@ -1238,24 +1204,24 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Figura 6.7: excluir os quadros em que a câmera não detecta o alvo (durante o giro), pois inflam o erro.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Implementado no relato dos resultados. A Seção 6.3.2 passou a reportar explicitamente dois regimes, com a nova Tabela 6.1: 'alvo em campo de visão' (mediana 1,28 m, RMSE 2,07 m), que é o número que caracteriza o estimador e passou a ser o valor de destaque, e 'todos os quadros' (mediana 1,75 m, RMSE 6,27 m), mantido para honestidade. O texto explica o critério de exclusão (teste de velocidade física acima de 4 m/s, disponível em tempo de execução) e por que incluir esses quadros mede a precisão do detector sob perda de visada, e não a capacidade de localização. Os números de destaque no Cap.8 foram atualizados na mesma direção.</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>O arquivo PDF da figura ainda traça a curva com todos os quadros; a legenda agora explicita os dois regimes e remete à tabela. Regerar o gráfico apenas com os quadros válidos depende dos dados da auditoria, que não estão nesta máquina.</t>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Implementado com um teste físico de visibilidade, e não mais com o heurístico de velocidade &gt; 4 m/s. Um quadro só conta como 'alvo em campo de visão' se (i) o raio retroprojetado da detecção intersecta o plano do chão à frente da câmera (lambda &gt; 0), (ii) o ponto no piso cai a no máximo 2 m do tatame topografado, e (iii) pelo menos um canto topografado do tatame projeta dentro da imagem 1280x960. O teste usa só intrínsecos, pose registrada e a geometria da sala — está disponível online e é o critério operacional que o sistema usaria para declarar perda de visada. Rejeita 106 dos 626 quadros com detecção (16,9%): 37 por raio que nunca atinge o piso e 69 por cair fora do tatame. As detecções rejeitadas ficam no alto da imagem (linha mediana v=185, contra 354 nas aceitas), acima do horizonte.</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Números atualizados: 'alvo em campo de visão' passou de mediana 1,28 m / RMSE 2,07 m (n=97, janelas de tempo ajustadas à mão) para mediana 1,43 m / RMSE 2,46 m (n=103, teste físico). 'Todos os quadros' permanece 1,75 m / 6,27 m (n=128), inalterado. Atualizados de forma consistente: Tabela 6.1, legendas das Figuras 6.6/6.7/6.8, Discussão do Cap.6 e o item correspondente do Cap.8.</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1231,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Inserir no texto a figura do equipamento utilizado na TU Berlin; ela só aparece nos slides.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Inserida a Figura 6.9 na Seção 6.2.7 (Experimental Platform), com a fotografia da plataforma UBADRON em voo dentro do ginásio onde os experimentos foram gravados.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Aproveitou-se para corrigir a descrição da montagem da câmera, que estava como "acima do centro do corpo" e é, de fato, em um casulo suspenso 0,21 m abaixo do corpo, inclinado 10° para baixo.</t>
         </is>
@@ -1292,24 +1258,24 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Indicar o hardware usado nos experimentos: laptop Dell i7 + RTX 4060; o tracker roda em tempo real, mas as inferências têm atraso de 2 a 3 s; não é possível rodar o pipeline completo em tempo real.</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Acrescentada a Seção 7.5.2 (Computational Setup) com a especificação da máquina e a caracterização honesta do que roda e do que não roda em tempo real, além de um parágrafo equivalente na Seção 6.2.7 para o estudo com dados reais. A limitação correspondente no Cap.8 foi reescrita para ficar consistente.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Confirmar o modelo exato do processador (i7-????) e a quantidade de memória RAM, caso se queira maior precisão na descrição.</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ATENÇÃO — hardware corrigido. A máquina onde estão TODOS os artefatos dos experimentos (runs/, dumps das 60 sequências, dataset, sessions/) é um Intel Core i9-13900HX com NVIDIA GeForce RTX 4080 Laptop GPU (12 GB), e não um i7 com RTX 4060 como anotado na defesa. Texto do Cap.7 (Seção 7.5.2) e do Cap.8 ajustados para o hardware real. CONFIRMAR com o autor se os experimentos foram mesmo rodados nesta máquina antes da entrega final.</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1285,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Indicar mais claramente que as nuvens de pontos são geradas por uma câmera de profundidade nos estudos II e III; sugerir o uso de LiDAR em trabalhos futuros.</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Criada a Seção 7.2.5 (Sensor Realism and the Limits of the Simulated Point Cloud), com um aviso explícito de que a nuvem provém de uma câmera de profundidade idealizada e não de um LiDAR, enumerando as diferenças (esparsidade, ruído, dropouts, atenuação atmosférica, oclusão e distorção por movimento) e declarando que as acurácias reportadas são um limite superior. Acrescentados o item correspondente nas Limitações e o item "Realistic range sensing" nos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1342,22 +1308,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Rastrear não basta para o avoid: é necessário predizer a trajetória futura alguns passos à frente.</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Reescrito o trecho da Seção 1.2 para afirmar que rastrear a posição atual é necessário mas não suficiente, explicando que a predição pode ser obtida propagando o estado (posição e velocidade) e sua covariância pelo modelo de movimento. Acrescentado item dedicado nas Limitações e o item "Trajectory prediction, and metrics that reward it" nos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1365,22 +1331,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Cuidado com a afirmação de que a profundidade não pode ser observada por câmeras: há redes modernas que a inferem de imagens monoculares.</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Afirmação suavizada no Cap.1: a profundidade passa a ser descrita como não observável "diretamente" a partir de uma única vista, com a ressalva explícita de que estimadores monoculares aprendidos recuperam profundidade métrica com acurácia útil, citando ZoeDepth e Depth Anything V2, e a diferença passa a ser colocada em termos de a inferência ser indireta e de erro mais difícil de caracterizar.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1388,22 +1354,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Destacar já na introdução de onde vêm as nuvens de pontos (LiDAR real ou sensor RGB-D).</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Criada a subseção 1.4.1 (Where the Point Clouds Come From), distinguindo os três casos: sensor genérico na arquitetura do Cap.4, câmera de profundidade idealizada do AirSim no Cap.7, e ausência de nuvem no Cap.6 (câmera monocular; o LiDAR só é usado offline para levantar o mapa de referência).</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1411,22 +1377,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Indicar as ferramentas e os motores de busca utilizados na busca inicial com o método PRISMA.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Seção 3.1.2 reescrita nomeando explicitamente as fontes (APIs do OpenAlex e do Semantic Scholar; busca acadêmica no Google Scholar, arXiv, IEEE Xplore, MDPI, SpringerLink e ScienceDirect), as famílias de consulta e os termos usados, e as ferramentas de gestão (Parsifal, Rayyan e Zotero), com referências bibliográficas para OpenAlex, Semantic Scholar e Rayyan.</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Acrescentado também um parágrafo de honestidade metodológica registrando que as buscas nas bases por assinatura (Scopus, Web of Science e IEEE Xplore institucional) foram preparadas mas não executadas, e por que o impacto disso é limitado.</t>
         </is>
@@ -1438,22 +1404,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Tentar publicar o que ainda não foi publicado.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Fora do escopo da correção do texto.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>O Cap.1 já registra que o estudo do Cap.6 está em preparação para publicação; o Cap.8 aponta o que falta para submeter o Cap.7 (benchmark externo e análise temporal).</t>
         </is>
@@ -1465,22 +1431,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Trabalho bem escrito, boa organização e boa metodologia (abordagem híbrida: detecção baseada em dados, rastreamento baseado em modelo).</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1492,22 +1458,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>(Pg. 34, Seção 2.3.3) O "tangent space of SE(3)" não existe como tal: o espaço tangente é definido em um ponto. Os elementos da álgebra de Lie são matrizes 4x4 parametrizadas por 6 números reais; o que se mostra é uma parametrização. Explicar o espaço isomórfico à álgebra de Lie.</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Seção 2.3.3 reescrita com rigor e retitulada "Pose Perturbations and the Lie Algebra of SE(3)": explica que SE(3) não é espaço vetorial mas grupo de Lie; que o espaço tangente é definido em um ponto e que o espaço tangente na identidade é a álgebra de Lie se(3); apresenta os elementos de se(3) como matrizes 4x4; define os mapas hat e vee como bijeções lineares e afirma o isomorfismo se(3) ≅ R^6; e explicita que o vetor de 6 componentes é o vetor de coordenadas de um elemento da álgebra, e não o próprio elemento.</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>O Apêndice A foi ajustado para usar a mesma linguagem.</t>
         </is>
@@ -1519,22 +1485,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Capítulo 5: destacar que não é feito joint (self) pose estimation and tracking.</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo na abertura do Cap.5 declarando que a pose da plataforma é entrada exógena conhecida, que o estado da plataforma nunca é aumentado no estado do filtro e que as medidas do alvo nunca realimentam a pose própria, com a justificativa (isolar a questão do referencial e espelhar a arquitetura real da aeronave).</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1542,22 +1508,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Qual a utilidade prática de ter um EKF no sistema local? Qual é a formulação preferida/recomendada?</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Criada a Seção 5.8 (Choice of Frame in Practice), que recomenda o referencial global como padrão (modelo exato, sem reorientação a implementar, estado diretamente interpretável a jusante) e enumera três situações concretas em que o local é preferível: ruído de processo referenciado ao corpo, ausência de posição global confiável (voo sem GNSS) e entrega direta das grandezas relativas que a camada de desvio consome.</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1565,22 +1531,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Figuras 5.1 e 5.3: o filtro está divergindo ou é um problema intrínseco? Deixar claro que tem a ver com o erro de distância, cuja variância é proporcional ao quadrado da distância.</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo logo após a Figura 5.1 explicando que não há divergência: o alvo se afasta ao longo do experimento e a variância do alcance cresce com o quadrado da distância, de modo que a informação por atualização diminui. A evidência decisiva é que o limite de Cramér-Rao posterior sobe com o mesmo perfil e o filtro o acompanha, ao passo que um filtro divergente se afastaria do limite.</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1588,22 +1554,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Indicar que é utilizado o rho predito para estimar o erro de distância, e comentar que isso viola as hipóteses do filtro de Kalman, pois há dependência entre o erro e o estado.</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Acrescentada a Observação 5.1 (State-dependent measurement noise), explicitando que R é avaliado no alcance predito, que isso viola a hipótese de ruído independente do estado, que o estimador é portanto subótimo, por que avaliar no alcance medido seria pior, e que o custo prático é pequeno e quantificado pela análise de Cramér-Rao.</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1611,22 +1577,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Equação 6.8: falta indicar a dedução. Expandir a seção mostrando como calcular o Jext, e definir melhor Hk e Jpi indicando as dimensões. Mencionar a aproximação exp(.) ≈ I + ...</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Seção 6.2.4 inteiramente reescrita em cinco passos numerados: (1) cadeia geométrica com as dimensões de cada fator; (2) Jacobiano de projeção Jpi (2x3) com a origem de cada termo; (3) Jacobiano de estado Hk (2x4) deduzido termo a termo; (4) Jacobiano extrínseco Jext (2x6), com a perturbação escrita multiplicativamente e a aproximação exp(xi^) = I + xi^ + ... ≈ I + xi^ explicitada, incluindo a ordem do resto; (5) dedução da covariância de inovação como soma de três formas quadráticas, com as dimensões anotadas sob cada termo e a hipótese de independência nomeada.</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Acrescentada ainda a interpretação do comportamento dos blocos rotacional e translacional com a distância, que explica por que o erro de atitude domina a longo alcance.</t>
         </is>
@@ -1638,22 +1604,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Figuras 6.5 e 6.7: os resultados não estão muito bons; deixar mais claro no texto como a dependência do erro em relação à distância e o giro do drone afetam os resultados. Discussão mais extensa e honesta, sem minimizar os problemas.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Discussão reescrita e ampliada. Foi acrescentada uma lista de três mecanismos distintos que contribuem para o erro (alcance, rotação da plataforma em dois canais separados, e precisão do detector sob perda de visada), a Tabela 6.1 com os dois regimes de relato, um parágrafo explicando como ler a Figura 6.7, e um parágrafo final na Discussão que diz sem rodeios o quanto esses números são e não são bons: uma ordem de grandeza acima do rastreador com sensor de alcance do Cap.5, com cauda pesada (p90 de 7,75 m), adequado para busca e salvamento e não, por si só, para anticolisão de curta distância.</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1661,22 +1627,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Explicar por que não temos o Sigma da pose da plataforma, já que deveria ser conhecido.</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Acrescentado o parágrafo "On the unavailability of Sigma" ao final da Seção 6.2.4, explicando que a solução de odometria LiDAR-inercial embarcada publica a pose mas não publica a covariância associada, que recuperá-la exigiria instrumentar e reexecutar a pilha de navegação, e que isso ficou fora do escopo da colaboração e inviável após o retorno ao Brasil. São declaradas as duas consequências: o termo captura a qualidade média da pose e não responde aos trechos de guinada rápida, e a isotropia é conveniência de modelagem e não afirmação física.</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1684,22 +1650,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Capítulo 7: indicar por que não utilizou o Jext para inflar o Sk com o Sigma da pose da plataforma, e sugerir como trabalho futuro.</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Acrescentados dois parágrafos ao final da Seção 7.3.7: a razão é que no simulador a pose é lida exatamente, de modo que o Sigma honesto é nulo e o termo se anula identicamente, e incluí-lo apenas introduziria um parâmetro ajustado sem referente físico. Em seguida se reconhece que a omissão é uma limitação real do estudo e se indica como o Jacobiano extrínseco seria montado para a medida esférica, remetendo aos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1707,24 +1673,24 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Figura 7.9: indicar métricas ao longo do tempo (comportamento temporal do erro); foram apresentadas apenas médias globais.</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>NÃO REALIZADO nesta versão.</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Os dados por quadro do Cap.7 (dumps de detecção das 60 sequências) não estão na máquina em que a revisão foi feita; estão na máquina de simulação do AirSim. A limitação foi registrada explicitamente no Cap.8 e o procedimento de geração está descrito para execução assim que houver acesso à máquina.</t>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>REALIZADO. Criada a Seção 7.6.4 (\label{sec:results-temporal}) com a nova Figura 7.x (Cap7/localization_over_time.pdf, \label{fig:temporal_error}), gerada por cap7_temporal.py a partir dos mesmos pares casados que produzem a Tabela 7.4 (mesmos dumps det_dumps_best, mesmo tracker SORT+EKF 3D, mesmo ponto de operação, mesmo gate 3D de 4 m), reindexados por quadro em vez de por faixa de alcance. Como as sequências têm comprimentos diferentes (50-92 quadros), a agregação é feita em tempo normalizado de sequência. Painel (a): mediana do erro 3D do centroide com banda interquartil e envelope do percentil 90; painel (b): CDF empírica por quadro, global e por ambiente.</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Resultado sobre 5.359 pares casados das 60 sequências: o erro é estacionário. A mediana por faixa fica entre 0,84 e 1,00 m do começo ao fim, e o envelope de p90 entre 1,43 e 1,91 m, sem deriva. Spearman rho = -0,10 (p&lt;0,001): significativo só pelo tamanho da amostra, magnitude desprezível e negativa. Kruskal-Wallis H=130 (p&lt;0,001) sobre 12 faixas, mas o efeito detectado abrange apenas 0,16 m de mediana. Não há transitório de inicialização visível (mediana dos 5 primeiros quadros 0,95 m vs 0,95 m no restante, Mann-Whitney p=0,53) — registrado no texto que isso se deve ao min_hits=3 do SORT, que esconde os dois primeiros quadros de cada track; o que se vê é uma melhora leve com a idade do track (0,99 m com 3 hits -&gt; 0,89 m com 8). Cap.8 atualizado.</t>
         </is>
       </c>
     </row>
@@ -1734,24 +1700,24 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Faltou uma referência global de comparação para as abordagens do Capítulo 7, antes de submeter os resultados para publicação.</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Registrado como limitação explícita no Cap.8 ("No comparison against an external benchmark") e como item de Trabalhos Futuros, indicando os dois caminhos concretos: avaliar no benchmark aéreo público UAV3D e reportar as linhas de base do domínio automotivo (KITTI e nuScenes) sobre as quais as famílias frustum e voxel foram originalmente validadas.</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>A execução da comparação depende da máquina de dados e está fora do prazo desta revisão; a lacuna, porém, deixou de ser silenciosa.</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Mantido como PARCIAL: a comparação externa NÃO foi executada. Avaliada a viabilidade nesta máquina e ela é inviável no prazo desta revisão — nenhum dos benchmarks (UAV3D, KITTI, nuScenes) está presente localmente, e o UAV3D é multi-câmera BEV construído sobre CARLA, sem a nuvem de pontos por frustum que este pipeline consome, de modo que seria preciso baixar centenas de GB, escrever um adaptador de dados para o rig de sensores deles e retreinar o estágio 2D para as classes do benchmark. Estimativa de esforço: da ordem de semanas de trabalho dedicado, não de horas. O texto do Cap.8 já é honesto sobre a lacuna (Limitações + Trabalhos Futuros com os três benchmarks nomeados), e por isso foi deixado como está.</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1727,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Deixar claro como é feita a associação de dados no trabalho.</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>A Seção 7.3.8 já descrevia a associação SORT com custo de IoU e atribuição pelo algoritmo húngaro no plano 2D, com os parâmetros na Tabela 7.3; o texto foi reforçado e o Cap.5 remete a ele.</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1784,22 +1750,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Trabalhos futuros devem considerar classes de objetos diferentes.</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Acrescentado o item "Multiple object classes" nos Trabalhos Futuros, apontando a extensão para detector multiclasse, modelos de movimento condicionados à classe (possivelmente por filtro de múltiplos modelos interagentes) e o efeito da identidade de classe como pista adicional de associação.</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1807,22 +1773,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Sugerir joint tracking e cooperative tracking; verificar se é aplicável a sense and avoid.</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Item de Trabalhos Futuros ampliado para distinguir rastreamento cooperativo (fusão de tracks) de estimação conjunta de pose e rastreamento cooperativos, com a ressalva de que a segunda introduz dependência do enlace de comunicação e correlação de erros que uma argumentação de certificação precisa endereçar.</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Incluída também a observação do Prof. Bruno sobre a filtragem centralizada criar um ponto único de falha.</t>
         </is>
@@ -1834,22 +1800,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Métricas bem definidas.</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1861,22 +1827,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Dado que o ruído no mundo real é anisotrópico, e apesar de as formulações serem equivalentes, por que não recomendar o EKF global?</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>A Seção 5.6.2 foi reescrita para deixar claro que o resultado é sobre casamento de referencial e não uma ordenação geral: o experimento reportado define o ruído no referencial inercial, o que favorece o global; ruído diagonal no referencial do corpo favorece o local pelo mesmo argumento. A Seção 5.8 então recomenda explicitamente o referencial global como padrão e enumera quando o local é preferível.</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1884,22 +1850,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>O recall baixo não seria compensado pelo tracker? As métricas MOTA e AMOTA sugerem isso?</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo na Discussão do Cap.7 que responde diretamente: a distância entre AMOTA alto (0,81) e MOTA baixo (0,44) é justamente a assinatura de um rastreador capaz alimentado por um detector limitado em recall, mas o AMOTA integra ao longo do eixo de recall e o coasting cobre lacunas de poucos quadros, não ausências prolongadas; um track nunca iniciado não pode ser propagado. Conclui-se que AMOTA é a métrica certa para comparar cadeias detector-rastreador e a errada para decidir quanto recall a função de anticolisão exige.</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr"/>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1907,22 +1873,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>Sem uma validação integrada (mesmo em simulação), é possível concluir qual é a abordagem mais promissora?</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo final de qualificação de escopo na Discussão do Cap.7: o que se compara é o front-end de detecção, cada variante integrada à mesma associação e filtragem e pontuada de ponta a ponta; o que não se avalia é a função completa de detectar e evitar. Declara-se que estabelecer a abordagem mais promissora nesse sentido exigiria fechar a malha e usar métricas preditivas e orientadas a risco.</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1930,22 +1896,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Qual seria a métrica apropriada para comparar as abordagens, dado que a tarefa exige predição da trajetória futura?</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Tratado no item "Trajectory prediction, and metrics that reward it" dos Trabalhos Futuros, que nomeia as métricas apropriadas: erro de deslocamento médio e final em um horizonte fixo, erro no tempo até o conflito ou até a aproximação máxima, e taxa de alertas de conflito perdidos ou espúrios.</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1953,22 +1919,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Quais os desafios para colocar o sistema em ambiente real?</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Os Capítulos 7 e 8 foram reforçados: restrições de processamento embarcado e ausência de orçamento de tempo real medido, lacuna sim-para-real do detector, idealização do sensor de profundidade, necessidade de coletar dados reais para ajuste fino, e propagação da incerteza de pose sob a solução de navegação real.</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1976,22 +1942,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Ser mais assertivo sobre qual abordagem é a melhor para sense and avoid.</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>A Discussão do Cap.7 passou de observação a recomendação explícita: recomenda-se o detector voxel de pilares aprendidos como detector primário, ou a fusão tardia frustum-voxel quando a precisão extra compensar, com os números que sustentam a escolha (recall 0,80 contra 0,49, e erro de localização menor, 0,87 m contra 1,05 m), e a ressalva de que o frustum continua preferível quando a estabilidade de identidade importa mais.</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1999,22 +1965,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>A previsão pode ser feita com base nas estimativas de posição e velocidade fornecidas pelo tracker.</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Incorporado ao texto da Seção 1.2: o estimador fornece a previsão na forma que um filtro recursivo naturalmente oferece, propagando o estado (posição e velocidade) e a covariância pelo modelo de movimento, com envelope de incerteza que se alarga com o horizonte.</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2022,22 +1988,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Deixar claro que a profundidade é fornecida por câmera RGB-D.</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Tratado na nova subseção 1.4.1 e na nova Seção 7.2.5, que declaram que a nuvem de trabalho do Cap.7 vem de uma câmera de profundidade planar idealizada do AirSim, e não do LiDAR simulado, com a justificativa (alvos vistos contra o céu, onde o LiDAR não retorna).</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2045,22 +2011,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>O Sigma não é estimado pela TU Berlin.</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Explicitado no parágrafo "On the unavailability of Sigma" da Seção 6.2.4: a solução de navegação publica a pose mas não a covariância.</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2068,22 +2034,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Local versus global: deixar mais claro por que o referencial local foi considerado, no contexto de sense and avoidance.</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Tratado na nova Seção 5.8, que dedica um parágrafo às três utilidades práticas do referencial local, incluindo o fato de que as grandezas que a camada de desvio consome (alcance relativo, azimute, elevação e velocidade de aproximação) são exatamente as grandezas do referencial local, entregues sem transformação e com a covariância no mesmo referencial.</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2091,22 +2057,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>A associação de dados é feita pelo SORT no plano 2D.</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Já explicitado na Seção 7.3.8 e reforçado; o Cap.5 remete a essa seção ao delimitar o escopo de alvo único.</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2114,22 +2080,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Deixar claro que o ruído anisotrópico é definido em coordenada global.</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Explicitado na Seção 5.6.2: o texto passa a dizer que a intensidade anisotrópica do experimento é especificada no referencial inercial global, e que é por isso que o filtro global modela o ruído corretamente.</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr"/>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2137,22 +2103,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Fazer uma planilha de acompanhamento das mudanças, para enviar à banca.</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Esta planilha.</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Gerada em CSV e XLSX em revisao-banca/.</t>
         </is>
@@ -2164,22 +2130,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Data da defesa no documento.</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Corrigida de 14 de julho de 2026 para 28 de julho de 2026 na folha de rosto e na Folha de Registro do Documento.</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2187,22 +2153,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Erros de ortografia e acentuação.</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Compilação verificada sem erros, sem referências indefinidas e com apenas uma linha de largura excedida (na tabela do próprio template do ITA). Lista de Abreviaturas ampliada de 22 para 49 entradas, cobrindo todas as siglas efetivamente usadas.</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2210,22 +2176,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Renumeração de figuras após as correções.</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>A inserção da fotografia da plataforma da TU Berlin (agora Figura 6.5) deslocou a numeração do Capítulo 6: a antiga Figura 6.6 (trajetória) passou a ser a Figura 6.7, e a antiga Figura 6.7 (erro e CDF) passou a ser a Figura 6.8.</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Registrado para que a banca consiga mapear as figuras citadas na arguição para a numeração da versão final.</t>
         </is>
@@ -2237,29 +2203,56 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Renomear "horizontal error" (decorrência: rótulos dos eixos das figuras).</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>Os rótulos internos dos arquivos PDF das Figuras 6.6 e 6.8 ainda trazem "horizontal localization error [m]" e "horizontal error [m]". O texto, as legendas e o Cap.8 já usam "ground-plane error".</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>Requer regerar os dois gráficos com o novo rótulo, o que depende dos dados do Cap.6 na máquina que os contém. É a única inconsistência visível remanescente entre texto e figura.</t>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>RESOLVIDO. As três figuras foram regeradas na máquina de dados pelo novo script cap6_figs_v2.py, com os rótulos corrigidos: 'horizontal error [m]' -&gt; 'Ground-plane error [m]' em Cap6/tracking_errors.pdf, e 'horizontal localization error [m]' -&gt; 'Ground-plane localization error [m]' em Cap6/error_vs_range.pdf. Cap6/tracking_traj.pdf também foi regerada (não tem rótulo de erro).</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Não resta nenhuma inconsistência entre texto e figura. Os nomes dos arquivos foram mantidos, de modo que as referências LaTeX não mudaram.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Geral (máquina de dados)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Reprodutibilidade das figuras do Cap.6 e do Cap.7.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Registrados no controle de versão os scripts que geram as figuras a partir dos dados brutos: ubaswarm_ws/src/tracker/src/tracker/cap6_figs_v2.py (Figuras 6.6, 6.7 e 6.8 do Cap.6, com o teste físico de visibilidade) e airsim/cap7_temporal.py (nova figura temporal do Cap.7). Regerado também o dump da ablação 'segmentação sem depth-band' (det_dumps_segnet_noband), que não existia mais em disco.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Conferência numérica completa do Cap.7 contra os dumps: mAP50 = 0,9949 (texto 0,994), 0,73/0,64 dos rótulos da API, cadeia de extração de foreground 2,94 -&gt; 2,87 -&gt; 1,20 -&gt; 1,05 m, precisão 0,21 -&gt; 0,90, AMOTA 0,04 -&gt; 0,81, Tabela 7.4 por ambiente (todos os 18 valores), Tabela 7.5 (PointPillars-PFN e fusão tardia, todos os 12 valores) e localização por faixa 1,25/1,16/1,30 m — todos reproduzidos exatamente. Dois ajustes: a ablação sem band deu 2,15 m (texto dizia 2,14 m) e a campanha tem 50-92 quadros por sequência a 2,7-5,1 Hz (o texto dizia 75-110 quadros a ~5 Hz). Único número não reverificável: o held-out dos voxel (AMOTA 0,67 / RMSE 0,85 m), porque o registro de qual split de 12 sequências foi usado não sobreviveu.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E71"/>
+  <autoFilter ref="A1:E72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>REALIZADO. Criada a Seção 7.6.4 (\label{sec:results-temporal}) com a nova Figura 7.x (Cap7/localization_over_time.pdf, \label{fig:temporal_error}), gerada por cap7_temporal.py a partir dos mesmos pares casados que produzem a Tabela 7.4 (mesmos dumps det_dumps_best, mesmo tracker SORT+EKF 3D, mesmo ponto de operação, mesmo gate 3D de 4 m), reindexados por quadro em vez de por faixa de alcance. Como as sequências têm comprimentos diferentes (50-92 quadros), a agregação é feita em tempo normalizado de sequência. Painel (a): mediana do erro 3D do centroide com banda interquartil e envelope do percentil 90; painel (b): CDF empírica por quadro, global e por ambiente.</t>
+          <t>REALIZADO. Criada a Seção 7.5.4 (\label{sec:results-temporal}) com a nova Figura 7.10 (Cap7/localization_over_time.pdf, \label{fig:temporal_error}), gerada por cap7_temporal.py a partir dos mesmos pares casados que produzem a Tabela 7.3 (mesmos dumps det_dumps_best, mesmo tracker SORT+EKF 3D, mesmo ponto de operação, mesmo gate 3D de 4 m), reindexados por quadro em vez de por faixa de alcance. Como as sequências têm comprimentos diferentes (50-92 quadros), a agregação é feita em tempo normalizado de sequência. Painel (a): mediana do erro 3D do centroide com banda interquartil e envelope do percentil 90; painel (b): CDF empírica por quadro, global e por ambiente.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Conferência numérica completa do Cap.7 contra os dumps: mAP50 = 0,9949 (texto 0,994), 0,73/0,64 dos rótulos da API, cadeia de extração de foreground 2,94 -&gt; 2,87 -&gt; 1,20 -&gt; 1,05 m, precisão 0,21 -&gt; 0,90, AMOTA 0,04 -&gt; 0,81, Tabela 7.4 por ambiente (todos os 18 valores), Tabela 7.5 (PointPillars-PFN e fusão tardia, todos os 12 valores) e localização por faixa 1,25/1,16/1,30 m — todos reproduzidos exatamente. Dois ajustes: a ablação sem band deu 2,15 m (texto dizia 2,14 m) e a campanha tem 50-92 quadros por sequência a 2,7-5,1 Hz (o texto dizia 75-110 quadros a ~5 Hz). Único número não reverificável: o held-out dos voxel (AMOTA 0,67 / RMSE 0,85 m), porque o registro de qual split de 12 sequências foi usado não sobreviveu.</t>
+          <t>Conferência numérica completa do Cap.7 contra os dumps: mAP50 = 0,9949 (texto 0,994), 0,73/0,64 dos rótulos da API, cadeia de extração de foreground 2,94 -&gt; 2,87 -&gt; 1,20 -&gt; 1,05 m, precisão 0,21 -&gt; 0,90, AMOTA 0,04 -&gt; 0,81, Tabela 7.3 por ambiente (todos os 18 valores), Tabela 7.4 (PointPillars-PFN e fusão tardia, todos os 12 valores) e localização por faixa 1,25/1,16/1,30 m — todos reproduzidos exatamente. Dois ajustes: a ablação sem band deu 2,15 m (texto dizia 2,14 m) e a campanha tem 50-92 quadros por sequência a 2,7-5,1 Hz (o texto dizia 75-110 quadros a ~5 Hz). Único número não reverificável: o held-out dos voxel (AMOTA 0,67 / RMSE 0,85 m), porque o registro de qual split de 12 sequências foi usado não sobreviveu.</t>
         </is>
       </c>
     </row>

--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Correções banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções banca'!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções banca'!$A$1:$E$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Registrado como limitação explícita no Cap.8 ("No comparison against an external benchmark") e como item de Trabalhos Futuros, indicando os dois caminhos concretos: avaliar no benchmark aéreo público UAV3D e reportar as linhas de base do domínio automotivo (KITTI e nuScenes) sobre as quais as famílias frustum e voxel foram originalmente validadas.</t>
+          <t>Tratado em duas frentes. (a) NÃO executado: a avaliação num benchmark público continua registrada como limitação explícita no Cap.8 e como primeiro item de Trabalhos Futuros, nomeando UAV3D (único aéreo 3D de larga escala), KITTI e nuScenes. (b) ACRESCENTADO ao Cap.7: uma quarta ressalva na Discussão que delimita como todo número do capítulo pode ser lido — a comparação é estritamente interna, e os valores de AMOTA/MOTA/IDF1 NÃO são comensuráveis com os valores publicados desses mesmos nomes em KITTI/nuScenes (classe única vs. benchmark multiclasse de tráfego, imagem sintética vs. real, profundidade densa idealizada vs. retorno de sensor real, e dificuldade definida pela nossa própria randomização). Diz explicitamente que AMOTA 0,81 nada afirma sobre posição em leaderboard público.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Mantido como PARCIAL: a comparação externa NÃO foi executada. Avaliada a viabilidade nesta máquina e ela é inviável no prazo desta revisão — nenhum dos benchmarks (UAV3D, KITTI, nuScenes) está presente localmente, e o UAV3D é multi-câmera BEV construído sobre CARLA, sem a nuvem de pontos por frustum que este pipeline consome, de modo que seria preciso baixar centenas de GB, escrever um adaptador de dados para o rig de sensores deles e retreinar o estágio 2D para as classes do benchmark. Estimativa de esforço: da ordem de semanas de trabalho dedicado, não de horas. O texto do Cap.8 já é honesto sobre a lacuna (Limitações + Trabalhos Futuros com os três benchmarks nomeados), e por isso foi deixado como está.</t>
+          <t>Decisão deliberada de NÃO citar números publicados de KITTI/nuScenes como âncora. Verificado que o AMOTA do nuScenes é média sobre múltiplas classes reais e varia de ~0,15 a ~0,77 conforme o detector usado — pôr esses valores lado a lado com 0,81 numa classe única sintética convidaria a leitura errada de que o resultado aéreo é superior, criando uma objeção nova onde hoje há uma lacuna honestamente declarada. Executar de fato no UAV3D é inviável no prazo: nada está local, e o UAV3D é multi-câmera BEV sobre CARLA, sem a nuvem por frustum que este pipeline consome — exigiria centenas de GB, um adaptador para o rig de sensores deles e retreino do estágio 2D. Estimativa: semanas.</t>
         </is>
       </c>
     </row>
@@ -2251,8 +2251,35 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Geral (máquina de dados)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Verificação do held-out dos detectores voxel (Seção 7.5.3).</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>CORRIGIDO — o texto estava errado. Recuperado o split determinístico no código de treino (pointpillars_pfn.py: sess=sorted(glob('sessions/*_seq*')); val=sess[::5]), ou seja 12 das 60 sequências, 4 por ambiente. Reavaliados os cinco modelos voxel só nessas 12, com o mesmo pipeline SORT+EKF 3D da Tabela 7.4. O texto afirmava que TODOS os resultados voxel concordavam com a campanha completa dentro de 0,02 AMOTA e 0,02 m de RMSE, e que o melhor modelo dava AMOTA 0,67 / RMSE 0,85 m no held-out. Ambas as afirmações são falsas.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Números reais (held-out vs. campanha completa): PointPillars hand-crafted 0,59 vs 0,63 AMOTA e 1,42 vs 1,19 m; grade fina 0,59 vs 0,60 e 1,28 vs 1,17 m; temporal 0,48 vs 0,51 e 1,69 vs 1,58 m; voxel 3D denso 0,67 vs 0,68 e 0,97 vs 0,92 m; PointPillars-PFN 0,67 vs 0,68 e 0,88 vs 0,87 m. O held-out é consistentemente PIOR em todos os cinco (0,005 a 0,048 AMOTA; 0,01 a 0,22 m RMSE), e o RMSE do melhor modelo é 0,88 m, não 0,85 m. O parágrafo foi reescrito para reportar o intervalo real, a direção do viés e o fato de o ranking se preservar, concluindo que as conclusões do capítulo se sustentam mas que os valores absolutos voxel da Tabela 7.4 são levemente otimistas. Conferidos de quebra os 30 valores voxel da Tabela 7.4 contra os dumps: todos exatos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E72"/>
+  <autoFilter ref="A1:E73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Correções banca" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções banca'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,6 +30,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00365F91"/>
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
     <fill>
@@ -54,7 +55,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -63,7 +64,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,26 +72,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,14 +478,14 @@
   <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Membro</t>
@@ -500,22 +518,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>(Capa) O nome do Prof. Maximo é sem acento.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Removido o acento em todas as ocorrências: capa/folha de rosto (tese.tex), agradecimentos, citação da publicação no Cap.1 e entrada do .bib.</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Confirmado com o autor. No registro oficial do ITA consta com acento; adotada a grafia sem acento conforme pedido da banca e conforme o professor assina suas publicações.</t>
         </is>
@@ -527,22 +545,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Fazer um Resumo e um Abstract mais didáticos; do jeito que estão, leigos não entenderão e poderão desistir da leitura.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Resumo e Abstract inteiramente reescritos em linguagem acessível: partem do cenário concreto (táxis aéreos e drones sobre cidades), explicam detect-and-avoid e as metades sense/avoid, descrevem os quatro estágios do pipeline em português/inglês simples e só então apresentam os três estudos e seus resultados.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>PreTextuais/resumo.tex e PreTextuais/abstract.tex. Criado também PreTextuais/resumo_frd.tex, versão condensada, pois o resumo completo não cabe na caixa de altura fixa da Folha de Registro do Documento.</t>
         </is>
@@ -554,22 +572,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>(Pg. 25) Colocar o significado da sigla GNSS na primeira aparição.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Primeira ocorrência (Cap.1, Seção 1.1.1) expandida para "Global Navigation Satellite System (GNSS)".</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>GNSS também acrescentado à Lista de Abreviaturas, que já o continha.</t>
         </is>
@@ -581,22 +599,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>(Pg. 27) Trocar "convolutional neural networks (CNNs)" por "Convolutional Neural Networks (CNNs)".</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Corrigido no Cap.1 e no Cap.2 ("A Convolutional Neural Network (CNN)").</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -604,22 +622,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>(Pg. 27 e 28) Acrescentar na Introdução uma Seção "Proposta de Solução", dividindo a Seção 1.3 em duas.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Seção 1.3 dividida: "1.3 Problem Statement" (problema e as três dificuldades) e a nova "1.4 Proposed Solution", que descreve o pipeline, traz a figura da arquitetura e a subseção "Where the Point Clouds Come From". As seções seguintes foram renumeradas automaticamente.</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -627,22 +645,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>(Pg. 30) Elogio à Seção sobre o uso de IA generativa no trabalho.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Sem ação necessária. A seção foi mantida (agora Seção 1.9).</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -654,22 +672,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>(Cap. 2) Ao apresentar as equações, ir dizendo onde elas serão utilizadas mais adiante.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Acrescentada ao final do Cap.2 a seção "Summary and Road Map", que percorre cada equação do capítulo e indica em qual capítulo posterior ela é usada (recursões do KF/EKF, convenções de referencial, perturbação em SE(3), modelo de velocidade constante, medida esférica, projeção pinhole, métricas e blocos de aprendizado). Adicionados também ponteiros pontuais ao longo do texto.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -677,22 +695,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>(Pg. 36 e 37) Trocar "root-mean-square error (RMSE)" por "Root-Mean-Square Error (RMSE)" e o mesmo para NEES, NIS, PCRB, TP, FP, FN, R, MOTA e CNN.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Todas as expansões corrigidas para caixa alta: RMSE, NEES, NIS, PCRB, True Positive (TP), False Positive (FP), False Negative (FN), Precision (P), Recall (R), MOTA, AMOTA, CNN, KF, BEV.</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Feita varredura automática em todos os arquivos .tex para localizar o padrão "expansão minúscula (SIGLA)".</t>
         </is>
@@ -704,22 +722,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>(Pg. 43) Primeira linha da Seção 3.3: uma palavra ultrapassa a margem direita.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Corrigido. A frase foi reescrita para eliminar o composto hifenizado que impedia a quebra, e foram acrescentados \tolerance=2000 e \emergencystretch=3em ao preâmbulo.</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Efeito global: as linhas com excesso de largura (overfull hbox) caíram de 14 para 1 — a única remanescente está na tabela da Folha de Registro, que é do próprio template do ITA.</t>
         </is>
@@ -731,22 +749,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Finalizar o Capítulo 3 (e todos os capítulos) com um parágrafo breve descrevendo o que será visto no capítulo seguinte.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Acrescentados parágrafos de encerramento com a transição para o capítulo seguinte nos Capítulos 2, 3, 5, 6 e 7. O Capítulo 4 já possuía; o Capítulo 8 é o último.</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>No Cap.3 o parágrafo foi reescrito para apontar para o Cap.4 (o capítulo seguinte), e não para o Cap.5.</t>
         </is>
@@ -758,22 +776,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>(Pg. 49) A Figura 4.1 demorou demais para aparecer; deveria estar já no Capítulo 1.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>A figura do pipeline foi inserida no Capítulo 1, dentro da nova Seção 1.4 (Proposed Solution), como Figura 1.2, com legenda remetendo ao Cap.4 para o detalhamento. A figura original foi mantida no Cap.4.</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -781,22 +799,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>(Pg. 53) Seções criadas sem texto introdutório antes da primeira subseção (ex.: 5.2 e 5.2.1); ocorre várias vezes no documento.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Localizadas por varredura automática as 12 ocorrências do padrão e inserido um parágrafo introdutório em todas: Cap.1 (Objectives), Cap.2 (3 seções), Cap.3 (2), Cap.5 (2, incluindo a 5.2 citada), Cap.6 (Results) e Cap.7 (3).</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -804,22 +822,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>(Pg. 54) Trocar "Constant-velocity (CV)" por "Constant-Velocity (CV)"; o mesmo para PCRB (pg. 61).</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Corrigido no Cap.2 e no Cap.5, e o PCRB corrigido no Cap.2, Cap.5 e Apêndice A.</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -827,22 +845,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Não sou especialista na área e não poderei revisar as equações.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Sem ação. As deduções foram, ainda assim, ampliadas e verificadas em resposta aos apontamentos do Prof. Bruno.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -850,22 +868,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>(Pg. 58) Elogio à formulação e à demonstração formal da Proposição 5.1.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Sem ação. Mantida.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -877,22 +895,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Elogio ao formalismo e aos resultados do Capítulo 5.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -904,22 +922,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>(Pg. 61) Deixar para dizer o que será feito no Capítulo 6 somente no último parágrafo do Capítulo 5, e não na penúltima seção.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>O anúncio do Cap.6 foi removido da Seção 5.6.3 e passou a ser o último parágrafo do capítulo, dentro da nova Seção 5.8 (Choice of Frame in Practice).</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>O anúncio do Cap.6 foi removido da Seção 5.7.3 e passou a ser o último parágrafo do capítulo, dentro da nova Seção 5.9 (Choice of Frame in Practice).</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -927,22 +945,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>(Pg. 77) Trocar "normalized innovation squared (NIS)" por caixa alta; idem RPC (pg. 82), PFN (pg. 91) e RMSE (pg. 94).</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Corrigidos: NIS (Cap.2 e Cap.6), Remote-Procedure-Call (RPC) e Pillar Feature Network (PFN) no Cap.7, e RMSE no Cap.7. Acrescentada também Set-Abstraction (SA).</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -950,22 +968,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Os Capítulos 7 e 8 estão adequados; o Capítulo 8 detalha bem limitações e melhorias futuras.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Sem ação corretiva. Ambos foram, mesmo assim, ampliados em resposta aos demais membros.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -977,22 +995,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>O Capítulo 6 está bastante adequado.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Sem ação corretiva. Ampliado conforme pedidos dos Profs. Alberto e Bruno.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1004,22 +1022,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Sugiro incluir o artigo clássico do algoritmo Adam (2014, arXiv).</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Referência de Kingma e Ba (ICLR 2015; arXiv:1412.6980, 2014) adicionada ao .bib e citada nos dois pontos em que o Adam é usado (Cap.7 e Apêndice B).</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1027,22 +1045,22 @@
           <t>Prof. Tasinaffo</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Parabéns pelo excelente trabalho.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1054,22 +1072,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Publicação em conferência Qualis A1; texto bem escrito; uso de IA adequado; boa apresentação.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1081,22 +1099,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Slide 35: o gráfico não é igual à Figura 6.6 da dissertação (p. 75). Ajustar na dissertação e explicar melhor a figura no texto.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Investigado e RESOLVIDO na máquina de dados. A figura da dissertação já era a versão corrigida pela auditoria de 06/06/2026 (commit 09505f0). Os scripts da auditoria estavam versionados no repositório do tracker (commit 4dee191: verify_projection.py, verify_ekf.py, cap6_figs.py) e reproduziram bit a bit todos os números publicados, de modo que as figuras 6.7 e 6.8 foram efetivamente regeradas a partir dos dados brutos (novo script cap6_figs_v2.py).</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Os slides continuam desatualizados e devem ser atualizados antes de qualquer reapresentação; a pasta 'DEFESA - SLIDES' não existe nesta máquina, então a regeração das figuras dos slides não pôde ser feita aqui. Verificada também a suspeita de que a curva de erro seria inconsistente com o gráfico de trajetória: NÃO há inconsistência. As duas foram conferidas amostra a amostra e coincidem exatamente; a aparência de contradição vinha de os estados divergentes (até (40,4; 17,4) m) caírem fora dos limites dos eixos do mapa. Registrado no texto (Seção 6.3.2).</t>
         </is>
@@ -1108,22 +1126,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>A legenda do EKF na Figura 6.6 está confusa; indicar que corresponde à barra de cor.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Legenda reescrita explicitando que a trajetória do EKF é colorida pelo tempo de voo e que a barra de cor à direita é a escala correspondente.</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1131,22 +1149,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Debater possíveis erros sistemáticos: giro do drone, erro na diagonal, erro devido à distância.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Ampliada a discussão de resultados do Cap.6 com a análise dos erros sistemáticos: dependência do erro com a distância (com a figura de erro versus alcance), efeito do ângulo de depressão rasante e o papel do giro em guinada, que é quando a pose de navegação é menos confiável e o alvo sai do campo de visão.</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1154,22 +1172,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Comentário geral: o texto não detalha suficientemente bem os resultados mostrados em gráficos (ex.: Figura 6.7).</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Discussão dos resultados do Cap.6 substancialmente ampliada, separando explicitamente a acurácia da geometria (projeção quadro a quadro) da robustez da cadeia completa, e explicando o que cada painel das figuras mostra.</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1177,22 +1195,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Renomear "horizontal error" para "erro no plano do chão" (ground-plane error).</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Termo renomeado para "ground-plane error" em todo o Cap.6 e no Cap.8, e acrescentado um parágrafo "Terminology" explicando que a medida é feita no plano do solo e não no plano da aeronave, e por que a componente vertical não é reportada.</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Os rótulos dos eixos dentro dos arquivos PDF das figuras serão atualizados na regeneração.</t>
         </is>
@@ -1204,22 +1222,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Figura 6.7: excluir os quadros em que a câmera não detecta o alvo (durante o giro), pois inflam o erro.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Implementado com um teste físico de visibilidade, e não mais com o heurístico de velocidade &gt; 4 m/s. Um quadro só conta como 'alvo em campo de visão' se (i) o raio retroprojetado da detecção intersecta o plano do chão à frente da câmera (lambda &gt; 0), (ii) o ponto no piso cai a no máximo 2 m do tatame topografado, e (iii) pelo menos um canto topografado do tatame projeta dentro da imagem 1280x960. O teste usa só intrínsecos, pose registrada e a geometria da sala — está disponível online e é o critério operacional que o sistema usaria para declarar perda de visada. Rejeita 106 dos 626 quadros com detecção (16,9%): 37 por raio que nunca atinge o piso e 69 por cair fora do tatame. As detecções rejeitadas ficam no alto da imagem (linha mediana v=185, contra 354 nas aceitas), acima do horizonte.</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Números atualizados: 'alvo em campo de visão' passou de mediana 1,28 m / RMSE 2,07 m (n=97, janelas de tempo ajustadas à mão) para mediana 1,43 m / RMSE 2,46 m (n=103, teste físico). 'Todos os quadros' permanece 1,75 m / 6,27 m (n=128), inalterado. Atualizados de forma consistente: Tabela 6.1, legendas das Figuras 6.6/6.7/6.8, Discussão do Cap.6 e o item correspondente do Cap.8.</t>
         </is>
@@ -1231,22 +1249,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Inserir no texto a figura do equipamento utilizado na TU Berlin; ela só aparece nos slides.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Inserida a Figura 6.9 na Seção 6.2.7 (Experimental Platform), com a fotografia da plataforma UBADRON em voo dentro do ginásio onde os experimentos foram gravados.</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Inserida a Figura 6.5 na Seção 6.2.6 (Experimental Platform), com a fotografia da plataforma UBADRON em voo dentro do ginásio onde os experimentos foram gravados.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Aproveitou-se para corrigir a descrição da montagem da câmera, que estava como "acima do centro do corpo" e é, de fato, em um casulo suspenso 0,21 m abaixo do corpo, inclinado 10° para baixo.</t>
         </is>
@@ -1258,24 +1276,24 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Indicar o hardware usado nos experimentos: laptop Dell i7 + RTX 4060; o tracker roda em tempo real, mas as inferências têm atraso de 2 a 3 s; não é possível rodar o pipeline completo em tempo real.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Acrescentada a Seção 7.5.2 (Computational Setup) com a especificação da máquina e a caracterização honesta do que roda e do que não roda em tempo real, além de um parágrafo equivalente na Seção 6.2.7 para o estudo com dados reais. A limitação correspondente no Cap.8 foi reescrita para ficar consistente.</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>ATENÇÃO — hardware corrigido. A máquina onde estão TODOS os artefatos dos experimentos (runs/, dumps das 60 sequências, dataset, sessions/) é um Intel Core i9-13900HX com NVIDIA GeForce RTX 4080 Laptop GPU (12 GB), e não um i7 com RTX 4060 como anotado na defesa. Texto do Cap.7 (Seção 7.5.2) e do Cap.8 ajustados para o hardware real. CONFIRMAR com o autor se os experimentos foram mesmo rodados nesta máquina antes da entrega final.</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Acrescentada a Seção 7.4.2 (Computational Setup) com a especificação da máquina e a caracterização honesta do que roda e do que não roda em tempo real, além de um parágrafo equivalente na Seção 6.2.6 para o estudo com dados reais. A limitação correspondente no Cap.8 foi reescrita para ficar consistente.</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Observação sobre o hardware: a máquina que contém todos os artefatos experimentais (runs de treino, dumps das 60 sequências, dataset e sessões de gravação) é um Intel Core i9-13900HX com NVIDIA GeForce RTX 4080 Laptop GPU (12 GB). A ata da defesa registrou "i7 + RTX 4060", que foi a resposta dada oralmente na sessão; o texto adota a especificação verificada nos artefatos. Seções 7.4.2, 6.2.6 e o Cap.8 estão consistentes entre si.</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1303,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Indicar mais claramente que as nuvens de pontos são geradas por uma câmera de profundidade nos estudos II e III; sugerir o uso de LiDAR em trabalhos futuros.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Criada a Seção 7.2.5 (Sensor Realism and the Limits of the Simulated Point Cloud), com um aviso explícito de que a nuvem provém de uma câmera de profundidade idealizada e não de um LiDAR, enumerando as diferenças (esparsidade, ruído, dropouts, atenuação atmosférica, oclusão e distorção por movimento) e declarando que as acurácias reportadas são um limite superior. Acrescentados o item correspondente nas Limitações e o item "Realistic range sensing" nos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1308,22 +1326,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Rastrear não basta para o avoid: é necessário predizer a trajetória futura alguns passos à frente.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Reescrito o trecho da Seção 1.2 para afirmar que rastrear a posição atual é necessário mas não suficiente, explicando que a predição pode ser obtida propagando o estado (posição e velocidade) e sua covariância pelo modelo de movimento. Acrescentado item dedicado nas Limitações e o item "Trajectory prediction, and metrics that reward it" nos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1331,22 +1349,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Cuidado com a afirmação de que a profundidade não pode ser observada por câmeras: há redes modernas que a inferem de imagens monoculares.</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Afirmação suavizada no Cap.1: a profundidade passa a ser descrita como não observável "diretamente" a partir de uma única vista, com a ressalva explícita de que estimadores monoculares aprendidos recuperam profundidade métrica com acurácia útil, citando ZoeDepth e Depth Anything V2, e a diferença passa a ser colocada em termos de a inferência ser indireta e de erro mais difícil de caracterizar.</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1354,22 +1372,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Destacar já na introdução de onde vêm as nuvens de pontos (LiDAR real ou sensor RGB-D).</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Criada a subseção 1.4.1 (Where the Point Clouds Come From), distinguindo os três casos: sensor genérico na arquitetura do Cap.4, câmera de profundidade idealizada do AirSim no Cap.7, e ausência de nuvem no Cap.6 (câmera monocular; o LiDAR só é usado offline para levantar o mapa de referência).</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1377,22 +1395,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Indicar as ferramentas e os motores de busca utilizados na busca inicial com o método PRISMA.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Seção 3.1.2 reescrita nomeando explicitamente as fontes (APIs do OpenAlex e do Semantic Scholar; busca acadêmica no Google Scholar, arXiv, IEEE Xplore, MDPI, SpringerLink e ScienceDirect), as famílias de consulta e os termos usados, e as ferramentas de gestão (Parsifal, Rayyan e Zotero), com referências bibliográficas para OpenAlex, Semantic Scholar e Rayyan.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Acrescentado também um parágrafo de honestidade metodológica registrando que as buscas nas bases por assinatura (Scopus, Web of Science e IEEE Xplore institucional) foram preparadas mas não executadas, e por que o impacto disso é limitado.</t>
         </is>
@@ -1404,22 +1422,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Tentar publicar o que ainda não foi publicado.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Fora do escopo da correção do texto.</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>O Cap.1 já registra que o estudo do Cap.6 está em preparação para publicação; o Cap.8 aponta o que falta para submeter o Cap.7 (benchmark externo e análise temporal).</t>
         </is>
@@ -1431,22 +1449,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Trabalho bem escrito, boa organização e boa metodologia (abordagem híbrida: detecção baseada em dados, rastreamento baseado em modelo).</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1458,22 +1476,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>(Pg. 34, Seção 2.3.3) O "tangent space of SE(3)" não existe como tal: o espaço tangente é definido em um ponto. Os elementos da álgebra de Lie são matrizes 4x4 parametrizadas por 6 números reais; o que se mostra é uma parametrização. Explicar o espaço isomórfico à álgebra de Lie.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Seção 2.3.3 reescrita com rigor e retitulada "Pose Perturbations and the Lie Algebra of SE(3)": explica que SE(3) não é espaço vetorial mas grupo de Lie; que o espaço tangente é definido em um ponto e que o espaço tangente na identidade é a álgebra de Lie se(3); apresenta os elementos de se(3) como matrizes 4x4; define os mapas hat e vee como bijeções lineares e afirma o isomorfismo se(3) ≅ R^6; e explicita que o vetor de 6 componentes é o vetor de coordenadas de um elemento da álgebra, e não o próprio elemento.</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>O Apêndice A foi ajustado para usar a mesma linguagem.</t>
         </is>
@@ -1485,22 +1503,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Capítulo 5: destacar que não é feito joint (self) pose estimation and tracking.</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo na abertura do Cap.5 declarando que a pose da plataforma é entrada exógena conhecida, que o estado da plataforma nunca é aumentado no estado do filtro e que as medidas do alvo nunca realimentam a pose própria, com a justificativa (isolar a questão do referencial e espelhar a arquitetura real da aeronave).</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1508,22 +1526,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>Qual a utilidade prática de ter um EKF no sistema local? Qual é a formulação preferida/recomendada?</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Criada a Seção 5.8 (Choice of Frame in Practice), que recomenda o referencial global como padrão (modelo exato, sem reorientação a implementar, estado diretamente interpretável a jusante) e enumera três situações concretas em que o local é preferível: ruído de processo referenciado ao corpo, ausência de posição global confiável (voo sem GNSS) e entrega direta das grandezas relativas que a camada de desvio consome.</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Criada a Seção 5.9 (Choice of Frame in Practice), que recomenda o referencial global como padrão (modelo exato, sem reorientação a implementar, estado diretamente interpretável a jusante) e enumera três situações concretas em que o local é preferível: ruído de processo referenciado ao corpo, ausência de posição global confiável (voo sem GNSS) e entrega direta das grandezas relativas que a camada de desvio consome.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1531,22 +1549,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Figuras 5.1 e 5.3: o filtro está divergindo ou é um problema intrínseco? Deixar claro que tem a ver com o erro de distância, cuja variância é proporcional ao quadrado da distância.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo logo após a Figura 5.1 explicando que não há divergência: o alvo se afasta ao longo do experimento e a variância do alcance cresce com o quadrado da distância, de modo que a informação por atualização diminui. A evidência decisiva é que o limite de Cramér-Rao posterior sobe com o mesmo perfil e o filtro o acompanha, ao passo que um filtro divergente se afastaria do limite.</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1554,22 +1572,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Indicar que é utilizado o rho predito para estimar o erro de distância, e comentar que isso viola as hipóteses do filtro de Kalman, pois há dependência entre o erro e o estado.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Acrescentada a Observação 5.1 (State-dependent measurement noise), explicitando que R é avaliado no alcance predito, que isso viola a hipótese de ruído independente do estado, que o estimador é portanto subótimo, por que avaliar no alcance medido seria pior, e que o custo prático é pequeno e quantificado pela análise de Cramér-Rao.</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Acrescentada a Observação 5.2 (State-dependent measurement noise), explicitando que R é avaliado no alcance predito, que isso viola a hipótese de ruído independente do estado, que o estimador é portanto subótimo, por que avaliar no alcance medido seria pior, e que o custo prático é pequeno e quantificado pela análise de Cramér-Rao.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1577,22 +1595,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Equação 6.8: falta indicar a dedução. Expandir a seção mostrando como calcular o Jext, e definir melhor Hk e Jpi indicando as dimensões. Mencionar a aproximação exp(.) ≈ I + ...</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Seção 6.2.4 inteiramente reescrita em cinco passos numerados: (1) cadeia geométrica com as dimensões de cada fator; (2) Jacobiano de projeção Jpi (2x3) com a origem de cada termo; (3) Jacobiano de estado Hk (2x4) deduzido termo a termo; (4) Jacobiano extrínseco Jext (2x6), com a perturbação escrita multiplicativamente e a aproximação exp(xi^) = I + xi^ + ... ≈ I + xi^ explicitada, incluindo a ordem do resto; (5) dedução da covariância de inovação como soma de três formas quadráticas, com as dimensões anotadas sob cada termo e a hipótese de independência nomeada.</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Acrescentada ainda a interpretação do comportamento dos blocos rotacional e translacional com a distância, que explica por que o erro de atitude domina a longo alcance.</t>
         </is>
@@ -1604,22 +1622,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Figuras 6.5 e 6.7: os resultados não estão muito bons; deixar mais claro no texto como a dependência do erro em relação à distância e o giro do drone afetam os resultados. Discussão mais extensa e honesta, sem minimizar os problemas.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Discussão reescrita e ampliada. Foi acrescentada uma lista de três mecanismos distintos que contribuem para o erro (alcance, rotação da plataforma em dois canais separados, e precisão do detector sob perda de visada), a Tabela 6.1 com os dois regimes de relato, um parágrafo explicando como ler a Figura 6.7, e um parágrafo final na Discussão que diz sem rodeios o quanto esses números são e não são bons: uma ordem de grandeza acima do rastreador com sensor de alcance do Cap.5, com cauda pesada (p90 de 7,75 m), adequado para busca e salvamento e não, por si só, para anticolisão de curta distância.</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1627,22 +1645,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Explicar por que não temos o Sigma da pose da plataforma, já que deveria ser conhecido.</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Acrescentado o parágrafo "On the unavailability of Sigma" ao final da Seção 6.2.4, explicando que a solução de odometria LiDAR-inercial embarcada publica a pose mas não publica a covariância associada, que recuperá-la exigiria instrumentar e reexecutar a pilha de navegação, e que isso ficou fora do escopo da colaboração e inviável após o retorno ao Brasil. São declaradas as duas consequências: o termo captura a qualidade média da pose e não responde aos trechos de guinada rápida, e a isotropia é conveniência de modelagem e não afirmação física.</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1650,22 +1668,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Capítulo 7: indicar por que não utilizou o Jext para inflar o Sk com o Sigma da pose da plataforma, e sugerir como trabalho futuro.</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Acrescentados dois parágrafos ao final da Seção 7.3.7: a razão é que no simulador a pose é lida exatamente, de modo que o Sigma honesto é nulo e o termo se anula identicamente, e incluí-lo apenas introduziria um parâmetro ajustado sem referente físico. Em seguida se reconhece que a omissão é uma limitação real do estudo e se indica como o Jacobiano extrínseco seria montado para a medida esférica, remetendo aos Trabalhos Futuros.</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1673,22 +1691,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Figura 7.9: indicar métricas ao longo do tempo (comportamento temporal do erro); foram apresentadas apenas médias globais.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>REALIZADO. Criada a Seção 7.5.4 (\label{sec:results-temporal}) com a nova Figura 7.10 (Cap7/localization_over_time.pdf, \label{fig:temporal_error}), gerada por cap7_temporal.py a partir dos mesmos pares casados que produzem a Tabela 7.3 (mesmos dumps det_dumps_best, mesmo tracker SORT+EKF 3D, mesmo ponto de operação, mesmo gate 3D de 4 m), reindexados por quadro em vez de por faixa de alcance. Como as sequências têm comprimentos diferentes (50-92 quadros), a agregação é feita em tempo normalizado de sequência. Painel (a): mediana do erro 3D do centroide com banda interquartil e envelope do percentil 90; painel (b): CDF empírica por quadro, global e por ambiente.</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Resultado sobre 5.359 pares casados das 60 sequências: o erro é estacionário. A mediana por faixa fica entre 0,84 e 1,00 m do começo ao fim, e o envelope de p90 entre 1,43 e 1,91 m, sem deriva. Spearman rho = -0,10 (p&lt;0,001): significativo só pelo tamanho da amostra, magnitude desprezível e negativa. Kruskal-Wallis H=130 (p&lt;0,001) sobre 12 faixas, mas o efeito detectado abrange apenas 0,16 m de mediana. Não há transitório de inicialização visível (mediana dos 5 primeiros quadros 0,95 m vs 0,95 m no restante, Mann-Whitney p=0,53) — registrado no texto que isso se deve ao min_hits=3 do SORT, que esconde os dois primeiros quadros de cada track; o que se vê é uma melhora leve com a idade do track (0,99 m com 3 hits -&gt; 0,89 m com 8). Cap.8 atualizado.</t>
         </is>
@@ -1700,22 +1718,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Faltou uma referência global de comparação para as abordagens do Capítulo 7, antes de submeter os resultados para publicação.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Tratado em duas frentes. (a) NÃO executado: a avaliação num benchmark público continua registrada como limitação explícita no Cap.8 e como primeiro item de Trabalhos Futuros, nomeando UAV3D (único aéreo 3D de larga escala), KITTI e nuScenes. (b) ACRESCENTADO ao Cap.7: uma quarta ressalva na Discussão que delimita como todo número do capítulo pode ser lido — a comparação é estritamente interna, e os valores de AMOTA/MOTA/IDF1 NÃO são comensuráveis com os valores publicados desses mesmos nomes em KITTI/nuScenes (classe única vs. benchmark multiclasse de tráfego, imagem sintética vs. real, profundidade densa idealizada vs. retorno de sensor real, e dificuldade definida pela nossa própria randomização). Diz explicitamente que AMOTA 0,81 nada afirma sobre posição em leaderboard público.</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Tratado em duas frentes. (a) NÃO executado: a avaliação num benchmark público continua registrada como limitação explícita no Cap.8 e como sexto item de Trabalhos Futuros, nomeando UAV3D (único aéreo 3D de larga escala), KITTI e nuScenes. (b) ACRESCENTADO ao Cap.7: uma quarta ressalva na Discussão que delimita como todo número do capítulo pode ser lido — a comparação é estritamente interna, e os valores de AMOTA/MOTA/IDF1 NÃO são comensuráveis com os valores publicados desses mesmos nomes em KITTI/nuScenes (classe única vs. benchmark multiclasse de tráfego, imagem sintética vs. real, profundidade densa idealizada vs. retorno de sensor real, e dificuldade definida pela nossa própria randomização). Diz explicitamente que AMOTA 0,81 nada afirma sobre posição em leaderboard público.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>PARCIAL</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Decisão deliberada de NÃO citar números publicados de KITTI/nuScenes como âncora. Verificado que o AMOTA do nuScenes é média sobre múltiplas classes reais e varia de ~0,15 a ~0,77 conforme o detector usado — pôr esses valores lado a lado com 0,81 numa classe única sintética convidaria a leitura errada de que o resultado aéreo é superior, criando uma objeção nova onde hoje há uma lacuna honestamente declarada. Executar de fato no UAV3D é inviável no prazo: nada está local, e o UAV3D é multi-câmera BEV sobre CARLA, sem a nuvem por frustum que este pipeline consome — exigiria centenas de GB, um adaptador para o rig de sensores deles e retreino do estágio 2D. Estimativa: semanas.</t>
         </is>
@@ -1727,22 +1745,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Deixar claro como é feita a associação de dados no trabalho.</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>A Seção 7.3.8 já descrevia a associação SORT com custo de IoU e atribuição pelo algoritmo húngaro no plano 2D, com os parâmetros na Tabela 7.3; o texto foi reforçado e o Cap.5 remete a ele.</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>A Seção 7.3.7 já descrevia a associação SORT com custo de IoU e atribuição pelo algoritmo húngaro no plano 2D, com os parâmetros na Tabela 7.3; o texto foi reforçado e o Cap.5 remete a ele.</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1750,22 +1768,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Trabalhos futuros devem considerar classes de objetos diferentes.</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Acrescentado o item "Multiple object classes" nos Trabalhos Futuros, apontando a extensão para detector multiclasse, modelos de movimento condicionados à classe (possivelmente por filtro de múltiplos modelos interagentes) e o efeito da identidade de classe como pista adicional de associação.</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1773,22 +1791,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Sugerir joint tracking e cooperative tracking; verificar se é aplicável a sense and avoid.</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Item de Trabalhos Futuros ampliado para distinguir rastreamento cooperativo (fusão de tracks) de estimação conjunta de pose e rastreamento cooperativos, com a ressalva de que a segunda introduz dependência do enlace de comunicação e correlação de erros que uma argumentação de certificação precisa endereçar.</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Incluída também a observação do Prof. Bruno sobre a filtragem centralizada criar um ponto único de falha.</t>
         </is>
@@ -1800,22 +1818,22 @@
           <t>Prof. Bruno</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>Métricas bem definidas.</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Sem ação.</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Elogio.</t>
         </is>
@@ -1827,22 +1845,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Dado que o ruído no mundo real é anisotrópico, e apesar de as formulações serem equivalentes, por que não recomendar o EKF global?</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>A Seção 5.6.2 foi reescrita para deixar claro que o resultado é sobre casamento de referencial e não uma ordenação geral: o experimento reportado define o ruído no referencial inercial, o que favorece o global; ruído diagonal no referencial do corpo favorece o local pelo mesmo argumento. A Seção 5.8 então recomenda explicitamente o referencial global como padrão e enumera quando o local é preferível.</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>A Seção 5.7.2 foi reescrita para deixar claro que o resultado é sobre casamento de referencial e não uma ordenação geral: o experimento reportado define o ruído no referencial inercial, o que favorece o global; ruído diagonal no referencial do corpo favorece o local pelo mesmo argumento. A Seção 5.9 então recomenda explicitamente o referencial global como padrão e enumera quando o local é preferível.</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1850,22 +1868,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>O recall baixo não seria compensado pelo tracker? As métricas MOTA e AMOTA sugerem isso?</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo na Discussão do Cap.7 que responde diretamente: a distância entre AMOTA alto (0,81) e MOTA baixo (0,44) é justamente a assinatura de um rastreador capaz alimentado por um detector limitado em recall, mas o AMOTA integra ao longo do eixo de recall e o coasting cobre lacunas de poucos quadros, não ausências prolongadas; um track nunca iniciado não pode ser propagado. Conclui-se que AMOTA é a métrica certa para comparar cadeias detector-rastreador e a errada para decidir quanto recall a função de anticolisão exige.</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1873,22 +1891,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Sem uma validação integrada (mesmo em simulação), é possível concluir qual é a abordagem mais promissora?</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Acrescentado parágrafo final de qualificação de escopo na Discussão do Cap.7: o que se compara é o front-end de detecção, cada variante integrada à mesma associação e filtragem e pontuada de ponta a ponta; o que não se avalia é a função completa de detectar e evitar. Declara-se que estabelecer a abordagem mais promissora nesse sentido exigiria fechar a malha e usar métricas preditivas e orientadas a risco.</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1896,22 +1914,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Qual seria a métrica apropriada para comparar as abordagens, dado que a tarefa exige predição da trajetória futura?</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Tratado no item "Trajectory prediction, and metrics that reward it" dos Trabalhos Futuros, que nomeia as métricas apropriadas: erro de deslocamento médio e final em um horizonte fixo, erro no tempo até o conflito ou até a aproximação máxima, e taxa de alertas de conflito perdidos ou espúrios.</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1919,22 +1937,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Quais os desafios para colocar o sistema em ambiente real?</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Os Capítulos 7 e 8 foram reforçados: restrições de processamento embarcado e ausência de orçamento de tempo real medido, lacuna sim-para-real do detector, idealização do sensor de profundidade, necessidade de coletar dados reais para ajuste fino, e propagação da incerteza de pose sob a solução de navegação real.</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1942,22 +1960,22 @@
           <t>Prof. Stiven</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Ser mais assertivo sobre qual abordagem é a melhor para sense and avoid.</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>A Discussão do Cap.7 passou de observação a recomendação explícita: recomenda-se o detector voxel de pilares aprendidos como detector primário, ou a fusão tardia frustum-voxel quando a precisão extra compensar, com os números que sustentam a escolha (recall 0,80 contra 0,49, e erro de localização menor, 0,87 m contra 1,05 m), e a ressalva de que o frustum continua preferível quando a estabilidade de identidade importa mais.</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1965,22 +1983,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>A previsão pode ser feita com base nas estimativas de posição e velocidade fornecidas pelo tracker.</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Incorporado ao texto da Seção 1.2: o estimador fornece a previsão na forma que um filtro recursivo naturalmente oferece, propagando o estado (posição e velocidade) e a covariância pelo modelo de movimento, com envelope de incerteza que se alarga com o horizonte.</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1988,22 +2006,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Deixar claro que a profundidade é fornecida por câmera RGB-D.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Tratado na nova subseção 1.4.1 e na nova Seção 7.2.5, que declaram que a nuvem de trabalho do Cap.7 vem de uma câmera de profundidade planar idealizada do AirSim, e não do LiDAR simulado, com a justificativa (alvos vistos contra o céu, onde o LiDAR não retorna).</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2011,22 +2029,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>O Sigma não é estimado pela TU Berlin.</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Explicitado no parágrafo "On the unavailability of Sigma" da Seção 6.2.4: a solução de navegação publica a pose mas não a covariância.</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2034,22 +2052,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Local versus global: deixar mais claro por que o referencial local foi considerado, no contexto de sense and avoidance.</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Tratado na nova Seção 5.8, que dedica um parágrafo às três utilidades práticas do referencial local, incluindo o fato de que as grandezas que a camada de desvio consome (alcance relativo, azimute, elevação e velocidade de aproximação) são exatamente as grandezas do referencial local, entregues sem transformação e com a covariância no mesmo referencial.</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Tratado na nova Seção 5.9, que dedica um parágrafo às três utilidades práticas do referencial local, incluindo o fato de que as grandezas que a camada de desvio consome (alcance relativo, azimute, elevação e velocidade de aproximação) são exatamente as grandezas do referencial local, entregues sem transformação e com a covariância no mesmo referencial.</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2057,22 +2075,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>A associação de dados é feita pelo SORT no plano 2D.</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Já explicitado na Seção 7.3.8 e reforçado; o Cap.5 remete a essa seção ao delimitar o escopo de alvo único.</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Já explicitado na Seção 7.3.7 e reforçado; o Cap.5 remete a essa seção ao delimitar o escopo de alvo único.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2080,22 +2098,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>Deixar claro que o ruído anisotrópico é definido em coordenada global.</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Explicitado na Seção 5.6.2: o texto passa a dizer que a intensidade anisotrópica do experimento é especificada no referencial inercial global, e que é por isso que o filtro global modela o ruído corretamente.</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Explicitado na Seção 5.7.2: o texto passa a dizer que a intensidade anisotrópica do experimento é especificada no referencial inercial global, e que é por isso que o filtro global modela o ruído corretamente.</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2103,22 +2121,22 @@
           <t>Prof. Maximo</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Fazer uma planilha de acompanhamento das mudanças, para enviar à banca.</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Esta planilha.</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Gerada em CSV e XLSX em revisao-banca/.</t>
         </is>
@@ -2130,22 +2148,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Data da defesa no documento.</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Corrigida de 14 de julho de 2026 para 28 de julho de 2026 na folha de rosto e na Folha de Registro do Documento.</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2153,22 +2171,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Erros de ortografia e acentuação.</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Compilação verificada sem erros, sem referências indefinidas e com apenas uma linha de largura excedida (na tabela do próprio template do ITA). Lista de Abreviaturas ampliada de 22 para 49 entradas, cobrindo todas as siglas efetivamente usadas.</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Compilação verificada sem erros, sem referências indefinidas e com apenas uma linha de largura excedida (na tabela do próprio template do ITA). Lista de Abreviaturas ampliada de 22 para 48 entradas, cobrindo todas as siglas efetivamente usadas.</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2176,22 +2194,22 @@
           <t>Geral</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Renumeração de figuras após as correções.</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>A inserção da fotografia da plataforma da TU Berlin (agora Figura 6.5) deslocou a numeração do Capítulo 6: a antiga Figura 6.6 (trajetória) passou a ser a Figura 6.7, e a antiga Figura 6.7 (erro e CDF) passou a ser a Figura 6.8.</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Registrado para que a banca consiga mapear as figuras citadas na arguição para a numeração da versão final.</t>
         </is>
@@ -2203,22 +2221,22 @@
           <t>Prof. Alberto</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Renomear "horizontal error" (decorrência: rótulos dos eixos das figuras).</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>RESOLVIDO. As três figuras foram regeradas na máquina de dados pelo novo script cap6_figs_v2.py, com os rótulos corrigidos: 'horizontal error [m]' -&gt; 'Ground-plane error [m]' em Cap6/tracking_errors.pdf, e 'horizontal localization error [m]' -&gt; 'Ground-plane localization error [m]' em Cap6/error_vs_range.pdf. Cap6/tracking_traj.pdf também foi regerada (não tem rótulo de erro).</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Não resta nenhuma inconsistência entre texto e figura. Os nomes dos arquivos foram mantidos, de modo que as referências LaTeX não mudaram.</t>
         </is>
@@ -2230,22 +2248,22 @@
           <t>Geral (máquina de dados)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>Reprodutibilidade das figuras do Cap.6 e do Cap.7.</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>Registrados no controle de versão os scripts que geram as figuras a partir dos dados brutos: ubaswarm_ws/src/tracker/src/tracker/cap6_figs_v2.py (Figuras 6.6, 6.7 e 6.8 do Cap.6, com o teste físico de visibilidade) e airsim/cap7_temporal.py (nova figura temporal do Cap.7). Regerado também o dump da ablação 'segmentação sem depth-band' (det_dumps_segnet_noband), que não existia mais em disco.</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Conferência numérica completa do Cap.7 contra os dumps: mAP50 = 0,9949 (texto 0,994), 0,73/0,64 dos rótulos da API, cadeia de extração de foreground 2,94 -&gt; 2,87 -&gt; 1,20 -&gt; 1,05 m, precisão 0,21 -&gt; 0,90, AMOTA 0,04 -&gt; 0,81, Tabela 7.3 por ambiente (todos os 18 valores), Tabela 7.4 (PointPillars-PFN e fusão tardia, todos os 12 valores) e localização por faixa 1,25/1,16/1,30 m — todos reproduzidos exatamente. Dois ajustes: a ablação sem band deu 2,15 m (texto dizia 2,14 m) e a campanha tem 50-92 quadros por sequência a 2,7-5,1 Hz (o texto dizia 75-110 quadros a ~5 Hz). Único número não reverificável: o held-out dos voxel (AMOTA 0,67 / RMSE 0,85 m), porque o registro de qual split de 12 sequências foi usado não sobreviveu.</t>
         </is>
@@ -2257,22 +2275,22 @@
           <t>Geral (máquina de dados)</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Verificação do held-out dos detectores voxel (Seção 7.5.3).</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Verificação do held-out dos detectores voxel (Seção 7.4.3).</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>CORRIGIDO — o texto estava errado. Recuperado o split determinístico no código de treino (pointpillars_pfn.py: sess=sorted(glob('sessions/*_seq*')); val=sess[::5]), ou seja 12 das 60 sequências, 4 por ambiente. Reavaliados os cinco modelos voxel só nessas 12, com o mesmo pipeline SORT+EKF 3D da Tabela 7.4. O texto afirmava que TODOS os resultados voxel concordavam com a campanha completa dentro de 0,02 AMOTA e 0,02 m de RMSE, e que o melhor modelo dava AMOTA 0,67 / RMSE 0,85 m no held-out. Ambas as afirmações são falsas.</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Números reais (held-out vs. campanha completa): PointPillars hand-crafted 0,59 vs 0,63 AMOTA e 1,42 vs 1,19 m; grade fina 0,59 vs 0,60 e 1,28 vs 1,17 m; temporal 0,48 vs 0,51 e 1,69 vs 1,58 m; voxel 3D denso 0,67 vs 0,68 e 0,97 vs 0,92 m; PointPillars-PFN 0,67 vs 0,68 e 0,88 vs 0,87 m. O held-out é consistentemente PIOR em todos os cinco (0,005 a 0,048 AMOTA; 0,01 a 0,22 m RMSE), e o RMSE do melhor modelo é 0,88 m, não 0,85 m. O parágrafo foi reescrito para reportar o intervalo real, a direção do viés e o fato de o ranking se preservar, concluindo que as conclusões do capítulo se sustentam mas que os valores absolutos voxel da Tabela 7.4 são levemente otimistas. Conferidos de quebra os 30 valores voxel da Tabela 7.4 contra os dumps: todos exatos.</t>
         </is>

--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -108,6 +113,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1293,7 +1301,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Observação sobre o hardware: a máquina que contém todos os artefatos experimentais (runs de treino, dumps das 60 sequências, dataset e sessões de gravação) é um Intel Core i9-13900HX com NVIDIA GeForce RTX 4080 Laptop GPU (12 GB). A ata da defesa registrou "i7 + RTX 4060", que foi a resposta dada oralmente na sessão; o texto adota a especificação verificada nos artefatos. Seções 7.4.2, 6.2.6 e o Cap.8 estão consistentes entre si.</t>
+          <t>Hardware confirmado pelo autor: Intel Core i9-13900HX com NVIDIA GeForce RTX 4080 Laptop GPU (12 GB), que é a máquina onde estão todos os artefatos experimentais. A ata da defesa registrou "i7 + RTX 4060", resposta dada oralmente na sessão; o texto adota a especificação verificada. Seções 7.4.2, 6.2.6 e o Cap.8 estão consistentes entre si.</t>
         </is>
       </c>
     </row>
@@ -2296,8 +2304,85 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Prof. Alberto</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Explicar melhor os resultados em gráficos (decorrência: leitura da figura de consistência do NIS).</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>O texto da Seção 6.3.3 e a legenda da Figura 6.10 foram reescritos para descrever o que a figura de fato mostra: o traço com a pose desligada oscila em torno do portão de 95% na parte inicial do registro e só depois se afasta em quatro a seis ordens de grandeza, e o traço calibrado permanece majoritariamente abaixo do valor consistente, ou seja, do lado conservador. As afirmações de "restaura a consistência" no Cap.6 e no Cap.8 foram suavizadas para "traz o filtro de volta ao regime consistente, errando para o lado conservador".</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>A figura em si não foi regerada, por decisão do autor. Fica registrado que o painel (b) usa o relógio bruto de aquisição da navegação, cuja origem difere do tempo de voo usado nas Figuras 6.7 e 6.8; isso está declarado na legenda para que os dois eixos não sejam lidos um contra o outro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Legibilidade da Figura 6.8.</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Nenhuma ação. O arquivo tem 792x288 pt e é incluído em 455 pt, ou seja, reduzido a 57%, de modo que os rótulos dos eixos saem em torno de 6 pt contra os 12 pt do corpo do texto.</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Decisão do autor de não regerar a figura. Corrigir exigiria apenas regerá-la em tamanho nativo menor (cerca de 480x200 pt), sem refazer nenhum cálculo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Reconciliação de medidas e afirmações não fundamentadas apontadas na auditoria final.</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Três ajustes: a área do tatame passou a ser reportada de forma única como 11,9 x 12,8 m, medida no local a partir do mapa LiDAR (antes aparecia também como 11,0 x 12,0 m); a afirmação de que o resultado "supera o GNSS de consumo" foi removida por não ter fonte e por comparar uma mediana com um valor RMS; e a velocidade máxima implícita de 3,8 m/s foi mantida conforme decisão do autor.</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>A Seção 7.3.7 já descrevia a associação SORT com custo de IoU e atribuição pelo algoritmo húngaro no plano 2D, com os parâmetros na Tabela 7.3; o texto foi reforçado e o Cap.5 remete a ele.</t>
+          <t>A Seção 7.3.7 já descrevia a associação SORT com custo de IoU e atribuição pelo algoritmo húngaro no plano 2D, com os parâmetros na Tabela 7.2; o texto foi reforçado e o Cap.5 remete a ele.</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>A inserção da fotografia da plataforma da TU Berlin (agora Figura 6.5) deslocou a numeração do Capítulo 6: a antiga Figura 6.6 (trajetória) passou a ser a Figura 6.7, e a antiga Figura 6.7 (erro e CDF) passou a ser a Figura 6.8.</t>
+          <t>Mapa de renumeração, para a banca localizar na versão final o que citou na arguição. Capítulo 6: a inserção da fotografia da plataforma da TU Berlin (agora Figura 6.5) deslocou as seguintes — a antiga Figura 6.5 (erro versus alcance) passou a 6.6, a antiga 6.6 (trajetória) passou a 6.7, e a antiga 6.7 (erro no tempo e CDF) passou a 6.8; a figura de consistência do NIS é a 6.10 e a nova Tabela 6.1 traz os dois regimes de relato. Capítulo 7: a Figura 7.9 citada pelo Prof. Bruno continua sendo a 7.9 (desempenho por ambiente e localização por alcance), a nova análise temporal é a Seção 7.5.4 com a Figura 7.10, e as tabelas da campanha são a 7.3 (por ambiente) e a 7.4 (comparação de arquiteturas); os parâmetros do rastreador estão na Tabela 7.2. Seções novas: 1.4 (Proposta de Solução), 5.9 (escolha do referencial), 7.2.5 (realismo do sensor) e 7.4.2 (ambiente computacional).</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2381,8 +2381,35 @@
       </c>
       <c r="E76" s="3" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Segunda auditoria cruzada, após a aplicação das correções.</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Foi feita uma segunda passagem adversarial sobre o texto já corrigido, com quatro auditores independentes (números do Cap.6, números do Cap.7, as figuras propriamente ditas e esta planilha). Foram corrigidos vinte itens, entre eles: uma afirmação de que os detectores voxel teriam IDF1 e MOTA menores, que a Tabela 7.4 contradiz (o MOTA deles é maior e não há IDF1 de voxel no documento); a duração do voo, que passou a distinguir a gravação de cerca de 150 s do trecho analisado de cerca de 90 s; a afirmação remanescente de degradação quadrática com o alcance na Discussão do Cap.6; faixas de recall, F1 e AMOTA que omitiam duas das cinco linhas voxel; e a verificação circular da extensão do tatame, removida.</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Também foi declarado no Cap.7 que apenas AMOTA e RMSE foram recomputados no subconjunto held-out, de modo que recall, precisão e F1 das linhas voxel permanecem valores in-sample, e que a linha de fusão tardia carrega o mesmo otimismo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E76"/>
+  <autoFilter ref="A1:E77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -113,9 +108,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2339,24 +2331,20 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Legibilidade da Figura 6.8.</t>
+          <t>Reconciliação de medidas e afirmações não fundamentadas apontadas na auditoria final.</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Nenhuma ação. O arquivo tem 792x288 pt e é incluído em 455 pt, ou seja, reduzido a 57%, de modo que os rótulos dos eixos saem em torno de 6 pt contra os 12 pt do corpo do texto.</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>Decisão do autor de não regerar a figura. Corrigir exigiria apenas regerá-la em tamanho nativo menor (cerca de 480x200 pt), sem refazer nenhum cálculo.</t>
-        </is>
-      </c>
+          <t>Três ajustes: a área do tatame passou a ser reportada de forma única como 11,9 x 12,8 m, medida no local a partir do mapa LiDAR (antes aparecia também como 11,0 x 12,0 m); a afirmação de que o resultado "supera o GNSS de consumo" foi removida por não ter fonte e por comparar uma mediana com um valor RMS; e a velocidade máxima implícita de 3,8 m/s foi mantida conforme decisão do autor.</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2366,12 +2354,12 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Reconciliação de medidas e afirmações não fundamentadas apontadas na auditoria final.</t>
+          <t>Segunda auditoria cruzada, após a aplicação das correções.</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Três ajustes: a área do tatame passou a ser reportada de forma única como 11,9 x 12,8 m, medida no local a partir do mapa LiDAR (antes aparecia também como 11,0 x 12,0 m); a afirmação de que o resultado "supera o GNSS de consumo" foi removida por não ter fonte e por comparar uma mediana com um valor RMS; e a velocidade máxima implícita de 3,8 m/s foi mantida conforme decisão do autor.</t>
+          <t>Foi feita uma segunda passagem adversarial sobre o texto já corrigido, com quatro auditores independentes (números do Cap.6, números do Cap.7, as figuras propriamente ditas e esta planilha). Foram corrigidos vinte itens, entre eles: uma afirmação de que os detectores voxel teriam IDF1 e MOTA menores, que a Tabela 7.4 contradiz (o MOTA deles é maior e não há IDF1 de voxel no documento); a duração do voo, que passou a distinguir a gravação de cerca de 150 s do trecho analisado de cerca de 90 s; a afirmação remanescente de degradação quadrática com o alcance na Discussão do Cap.6; faixas de recall, F1 e AMOTA que omitiam duas das cinco linhas voxel; e a verificação circular da extensão do tatame, removida.</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -2379,37 +2367,14 @@
           <t>SIM</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Geral</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Segunda auditoria cruzada, após a aplicação das correções.</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>Foi feita uma segunda passagem adversarial sobre o texto já corrigido, com quatro auditores independentes (números do Cap.6, números do Cap.7, as figuras propriamente ditas e esta planilha). Foram corrigidos vinte itens, entre eles: uma afirmação de que os detectores voxel teriam IDF1 e MOTA menores, que a Tabela 7.4 contradiz (o MOTA deles é maior e não há IDF1 de voxel no documento); a duração do voo, que passou a distinguir a gravação de cerca de 150 s do trecho analisado de cerca de 90 s; a afirmação remanescente de degradação quadrática com o alcance na Discussão do Cap.6; faixas de recall, F1 e AMOTA que omitiam duas das cinco linhas voxel; e a verificação circular da extensão do tatame, removida.</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Também foi declarado no Cap.7 que apenas AMOTA e RMSE foram recomputados no subconjunto held-out, de modo que recall, precisão e F1 das linhas voxel permanecem valores in-sample, e que a linha de fusão tardia carrega o mesmo otimismo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E77"/>
+  <autoFilter ref="A1:E76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tratado em duas frentes. (a) NÃO executado: a avaliação num benchmark público continua registrada como limitação explícita no Cap.8 e como sexto item de Trabalhos Futuros, nomeando UAV3D (único aéreo 3D de larga escala), KITTI e nuScenes. (b) ACRESCENTADO ao Cap.7: uma quarta ressalva na Discussão que delimita como todo número do capítulo pode ser lido — a comparação é estritamente interna, e os valores de AMOTA/MOTA/IDF1 NÃO são comensuráveis com os valores publicados desses mesmos nomes em KITTI/nuScenes (classe única vs. benchmark multiclasse de tráfego, imagem sintética vs. real, profundidade densa idealizada vs. retorno de sensor real, e dificuldade definida pela nossa própria randomização). Diz explicitamente que AMOTA 0,81 nada afirma sobre posição em leaderboard público.</t>
+          <t>Tratado em duas frentes. (a) A avaliação num benchmark público está indicada como item de Trabalhos Futuros no Cap.8, nomeando o UAV3D (único aéreo 3D de larga escala), o KITTI e o nuScenes, com o caminho concreto: rodar o próprio pipeline ponta a ponta nesses conjuntos, e não apenas citar números publicados. (b) Acrescentada ao Cap.7 uma ressalva na Discussão que delimita como todo número do capítulo pode ser lido: a comparação é estritamente interna, e os valores de AMOTA, MOTA e IDF1 não são comensuráveis com os valores publicados desses mesmos nomes em KITTI ou nuScenes (classe única contra benchmark multiclasse de tráfego real, imagem sintética, profundidade idealizada, e dificuldade definida pela randomização deste trabalho). Diz explicitamente que um AMOTA de 0,81 nada afirma sobre posição em leaderboard público.</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Decisão deliberada de NÃO citar números publicados de KITTI/nuScenes como âncora. Verificado que o AMOTA do nuScenes é média sobre múltiplas classes reais e varia de ~0,15 a ~0,77 conforme o detector usado — pôr esses valores lado a lado com 0,81 numa classe única sintética convidaria a leitura errada de que o resultado aéreo é superior, criando uma objeção nova onde hoje há uma lacuna honestamente declarada. Executar de fato no UAV3D é inviável no prazo: nada está local, e o UAV3D é multi-câmera BEV sobre CARLA, sem a nuvem por frustum que este pipeline consome — exigiria centenas de GB, um adaptador para o rig de sensores deles e retreino do estágio 2D. Estimativa: semanas.</t>
+          <t>Decisão deliberada de não citar números publicados de KITTI/nuScenes como âncora: o AMOTA do nuScenes é média sobre múltiplas classes reais e varia de cerca de 0,15 a 0,77 conforme o detector, de modo que pô-los ao lado de 0,81 numa classe única sintética convidaria à leitura errada de que o resultado aéreo é superior. Executar no UAV3D não é viável no prazo: o benchmark é multi-câmera BEV sobre CARLA, sem a nuvem por frustum que este pipeline consome, e exigiria adaptar o rig de sensores e retreinar o estágio 2D.</t>
         </is>
       </c>
     </row>

--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2323,58 +2323,8 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Geral</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Reconciliação de medidas e afirmações não fundamentadas apontadas na auditoria final.</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>Três ajustes: a área do tatame passou a ser reportada de forma única como 11,9 x 12,8 m, medida no local a partir do mapa LiDAR (antes aparecia também como 11,0 x 12,0 m); a afirmação de que o resultado "supera o GNSS de consumo" foi removida por não ter fonte e por comparar uma mediana com um valor RMS; e a velocidade máxima implícita de 3,8 m/s foi mantida conforme decisão do autor.</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Geral</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Segunda auditoria cruzada, após a aplicação das correções.</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>Foi feita uma segunda passagem adversarial sobre o texto já corrigido, com quatro auditores independentes (números do Cap.6, números do Cap.7, as figuras propriamente ditas e esta planilha). Foram corrigidos vinte itens, entre eles: uma afirmação de que os detectores voxel teriam IDF1 e MOTA menores, que a Tabela 7.4 contradiz (o MOTA deles é maior e não há IDF1 de voxel no documento); a duração do voo, que passou a distinguir a gravação de cerca de 150 s do trecho analisado de cerca de 90 s; a afirmação remanescente de degradação quadrática com o alcance na Discussão do Cap.6; faixas de recall, F1 e AMOTA que omitiam duas das cinco linhas voxel; e a verificação circular da extensão do tatame, removida.</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>Também foi declarado no Cap.7 que apenas AMOTA e RMSE foram recomputados no subconjunto held-out, de modo que recall, precisão e F1 das linhas voxel permanecem valores in-sample, e que a linha de fusão tardia carrega o mesmo otimismo.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E76"/>
+  <autoFilter ref="A1:E74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/revisao-banca/correcoes-banca.xlsx
+++ b/revisao-banca/correcoes-banca.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correções da banca" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Correções da banca'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2323,8 +2323,35 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Prof. Maximo</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Retirar o bloco do Pró-Reitor da folha de rosto.</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Bloco removido. O template novo do ITA não traz mais o nome do Pró-Reitor de Pós-Graduação na folha de rosto; a classe ita.cls do Overleaf ainda o imprime, então o campo foi suprimido no tese.tex. A folha de rosto passou a terminar em orientador e coorientador.</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Antes disso o nome havia sido corrigido de Antonio Guilherme de Arruda Lorenzi para André Valdetaro Gomes Cavalieri, o titular atual; com a remoção do bloco, a correção deixou de ser necessária, mas fica registrada no tese.tex em comentário caso o campo volte a ser exigido.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E74"/>
+  <autoFilter ref="A1:E75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>